--- a/Project_Naive_Bayes_Demonstration.xlsx
+++ b/Project_Naive_Bayes_Demonstration.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Inputs" sheetId="1" state="visible" r:id="rId3"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="743" uniqueCount="345">
   <si>
     <t xml:space="preserve">Email Input</t>
   </si>
@@ -116,14 +116,6 @@
   </si>
   <si>
     <t xml:space="preserve">Final UI probabilities shown by the project.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P(fraud | features)=exp_score(fraud)/[exp_score(fraud)+exp_score(injection)+exp_score(safe)]
-P(injection | features)=exp_score(injection)/[exp_score(fraud)+exp_score(injection)+exp_score(safe)]
-P(safe | features)=exp_score(safe)/[exp_score(fraud)+exp_score(injection)+exp_score(safe)]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">predicted_label = class with highest raw log score: fraud, injection, or safe</t>
   </si>
   <si>
     <t xml:space="preserve">Model Parameters From Dataset</t>
@@ -1096,7 +1088,7 @@
     <numFmt numFmtId="166" formatCode="0.000000"/>
     <numFmt numFmtId="167" formatCode="0.0000%"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1149,12 +1141,6 @@
       <name val="Aptos"/>
       <family val="0"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="7">
@@ -1249,64 +1235,60 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1566,7 +1548,7 @@
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="94.04"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="94.03"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="50"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
   </cols>
@@ -1687,14 +1669,10 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="81.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="8" t="s">
-        <v>25</v>
-      </c>
+      <c r="B14" s="8"/>
     </row>
     <row r="15" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="8" t="s">
-        <v>26</v>
-      </c>
+      <c r="B15" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1726,7 +1704,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1749,24 +1727,24 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="D4" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="E4" s="5" t="s">
         <v>30</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B5" s="6" t="n">
         <v>3333</v>
@@ -1778,12 +1756,12 @@
         <v>3334</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B6" s="6" t="n">
         <v>10000</v>
@@ -1795,12 +1773,12 @@
         <v>10000</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B7" s="9" t="n">
         <f aca="false">B5/B6</f>
@@ -1815,12 +1793,12 @@
         <v>0.3334</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B8" s="9" t="n">
         <f aca="false">LN(B7)</f>
@@ -1835,12 +1813,12 @@
         <v>-1.09841230866544</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B9" s="6" t="n">
         <v>1168629</v>
@@ -1852,12 +1830,12 @@
         <v>219954</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B10" s="6" t="n">
         <v>6874</v>
@@ -1869,12 +1847,12 @@
         <v>6874</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B11" s="6" t="n">
         <v>1</v>
@@ -1886,12 +1864,12 @@
         <v>1</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B12" s="6" t="n">
         <v>0.2</v>
@@ -1903,12 +1881,12 @@
         <v>0.2</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B13" s="6" t="n">
         <v>10</v>
@@ -1920,7 +1898,7 @@
         <v>10</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -1957,7 +1935,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1986,35 +1964,35 @@
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="D4" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="E4" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="F4" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="G4" s="5" t="s">
         <v>56</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C5" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C5" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A5,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>1</v>
       </c>
@@ -2029,17 +2007,17 @@
         <v>2</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C6" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C6" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A6,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>1</v>
       </c>
@@ -2054,17 +2032,17 @@
         <v>2</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C7" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C7" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A7,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -2081,17 +2059,17 @@
         <v>0</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C8" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C8" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A8,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -2108,17 +2086,17 @@
         <v>0</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C9" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C9" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A9,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -2135,17 +2113,17 @@
         <v>0</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C10" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C10" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A10,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -2162,17 +2140,17 @@
         <v>0</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C11" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C11" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A11,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -2189,17 +2167,17 @@
         <v>0</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C12" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C12" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A12,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -2216,17 +2194,17 @@
         <v>0</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C13" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C13" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A13,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -2243,17 +2221,17 @@
         <v>0</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C14" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C14" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A14,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -2270,17 +2248,17 @@
         <v>0</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C15" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C15" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A15,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>1</v>
       </c>
@@ -2295,17 +2273,17 @@
         <v>2</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C16" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C16" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A16,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -2322,17 +2300,17 @@
         <v>0</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C17" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C17" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A17,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>1</v>
       </c>
@@ -2347,17 +2325,17 @@
         <v>2</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C18" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C18" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A18,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -2374,17 +2352,17 @@
         <v>0</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C19" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C19" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A19,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -2401,17 +2379,17 @@
         <v>0</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C20" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C20" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A20,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -2428,17 +2406,17 @@
         <v>0</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C21" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C21" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A21,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -2455,17 +2433,17 @@
         <v>0</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C22" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C22" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A22,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>1</v>
       </c>
@@ -2480,17 +2458,17 @@
         <v>2</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C23" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C23" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A23,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>1</v>
       </c>
@@ -2505,17 +2483,17 @@
         <v>2</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C24" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C24" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A24,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -2532,17 +2510,17 @@
         <v>0</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C25" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C25" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A25,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -2559,17 +2537,17 @@
         <v>0</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C26" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C26" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A26,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -2586,17 +2564,17 @@
         <v>0</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C27" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C27" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A27,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -2613,17 +2591,17 @@
         <v>0</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C28" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C28" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A28,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -2640,17 +2618,17 @@
         <v>0</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C29" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C29" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A29,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -2667,17 +2645,17 @@
         <v>0</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C30" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C30" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A30,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -2694,17 +2672,17 @@
         <v>0</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C31" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C31" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A31,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -2721,17 +2699,17 @@
         <v>0</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C32" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C32" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A32,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -2748,17 +2726,17 @@
         <v>0</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C33" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C33" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A33,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -2775,17 +2753,17 @@
         <v>0</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C34" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C34" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A34,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -2802,17 +2780,17 @@
         <v>0</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C35" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C35" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A35,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>1</v>
       </c>
@@ -2827,17 +2805,17 @@
         <v>2</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C36" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C36" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A36,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -2854,17 +2832,17 @@
         <v>0</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C37" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C37" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A37,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -2881,17 +2859,17 @@
         <v>0</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C38" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C38" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A38,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -2908,17 +2886,17 @@
         <v>0</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C39" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C39" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A39,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -2935,17 +2913,17 @@
         <v>0</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C40" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C40" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A40,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -2962,17 +2940,17 @@
         <v>0</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C41" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C41" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A41,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -2989,17 +2967,17 @@
         <v>0</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C42" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C42" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A42,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>1</v>
       </c>
@@ -3014,17 +2992,17 @@
         <v>2</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C43" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C43" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A43,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>1</v>
       </c>
@@ -3039,17 +3017,17 @@
         <v>2</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C44" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C44" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A44,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -3066,17 +3044,17 @@
         <v>0</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C45" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C45" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A45,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -3093,17 +3071,17 @@
         <v>0</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C46" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C46" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A46,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -3120,17 +3098,17 @@
         <v>0</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C47" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C47" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A47,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -3147,17 +3125,17 @@
         <v>0</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C48" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C48" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A48,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -3174,17 +3152,17 @@
         <v>0</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C49" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C49" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A49,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -3201,17 +3179,17 @@
         <v>0</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C50" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C50" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A50,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -3228,17 +3206,17 @@
         <v>0</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C51" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C51" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A51,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -3255,17 +3233,17 @@
         <v>0</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C52" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C52" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A52,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -3282,17 +3260,17 @@
         <v>0</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C53" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C53" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A53,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -3309,17 +3287,17 @@
         <v>0</v>
       </c>
       <c r="G53" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C54" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C54" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A54,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -3336,17 +3314,17 @@
         <v>0</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C55" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C55" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A55,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -3363,17 +3341,17 @@
         <v>0</v>
       </c>
       <c r="G55" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C56" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C56" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A56,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>1</v>
       </c>
@@ -3388,17 +3366,17 @@
         <v>2</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C57" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C57" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A57,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -3415,17 +3393,17 @@
         <v>0</v>
       </c>
       <c r="G57" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C58" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C58" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A58,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -3442,17 +3420,17 @@
         <v>0</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="6" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C59" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C59" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A59,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>1</v>
       </c>
@@ -3467,17 +3445,17 @@
         <v>2</v>
       </c>
       <c r="G59" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C60" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C60" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A60,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -3494,17 +3472,17 @@
         <v>0</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C61" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C61" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A61,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -3521,17 +3499,17 @@
         <v>0</v>
       </c>
       <c r="G61" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C62" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C62" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A62,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>1</v>
       </c>
@@ -3546,17 +3524,17 @@
         <v>2</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C63" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C63" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A63,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -3573,17 +3551,17 @@
         <v>0</v>
       </c>
       <c r="G63" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C64" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C64" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A64,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -3600,17 +3578,17 @@
         <v>0</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C65" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C65" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A65,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -3627,17 +3605,17 @@
         <v>0</v>
       </c>
       <c r="G65" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C66" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C66" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A66,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -3654,17 +3632,17 @@
         <v>0</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C67" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C67" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A67,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -3681,17 +3659,17 @@
         <v>0</v>
       </c>
       <c r="G67" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C68" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C68" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A68,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -3708,17 +3686,17 @@
         <v>0</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C69" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C69" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A69,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -3735,17 +3713,17 @@
         <v>0</v>
       </c>
       <c r="G69" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C70" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C70" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A70,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>1</v>
       </c>
@@ -3760,17 +3738,17 @@
         <v>2</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="6" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C71" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C71" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A71,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -3787,17 +3765,17 @@
         <v>0</v>
       </c>
       <c r="G71" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="6" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C72" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C72" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A72,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -3814,17 +3792,17 @@
         <v>0</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="6" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C73" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C73" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A73,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -3841,17 +3819,17 @@
         <v>0</v>
       </c>
       <c r="G73" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C74" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C74" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A74,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -3868,17 +3846,17 @@
         <v>0</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C75" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C75" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A75,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -3895,17 +3873,17 @@
         <v>0</v>
       </c>
       <c r="G75" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="6" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C76" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C76" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A76,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -3922,17 +3900,17 @@
         <v>0</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="6" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C77" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C77" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A77,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -3949,17 +3927,17 @@
         <v>0</v>
       </c>
       <c r="G77" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="6" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C78" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C78" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A78,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -3976,17 +3954,17 @@
         <v>0</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C79" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C79" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A79,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>1</v>
       </c>
@@ -4001,17 +3979,17 @@
         <v>2</v>
       </c>
       <c r="G79" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="6" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C80" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C80" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A80,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -4028,17 +4006,17 @@
         <v>0</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="6" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C81" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C81" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A81,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -4055,17 +4033,17 @@
         <v>0</v>
       </c>
       <c r="G81" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="6" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C82" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C82" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A82,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>1</v>
       </c>
@@ -4080,17 +4058,17 @@
         <v>2</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="6" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C83" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C83" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A83,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -4107,17 +4085,17 @@
         <v>0</v>
       </c>
       <c r="G83" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="6" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C84" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C84" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A84,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -4134,17 +4112,17 @@
         <v>0</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="6" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C85" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C85" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A85,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -4161,17 +4139,17 @@
         <v>0</v>
       </c>
       <c r="G85" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C86" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C86" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A86,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -4188,17 +4166,17 @@
         <v>0</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C87" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C87" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A87,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -4215,17 +4193,17 @@
         <v>0</v>
       </c>
       <c r="G87" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C88" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C88" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A88,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -4242,17 +4220,17 @@
         <v>0</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C89" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C89" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A89,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -4269,17 +4247,17 @@
         <v>0</v>
       </c>
       <c r="G89" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="6" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C90" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C90" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A90,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -4296,17 +4274,17 @@
         <v>0</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C91" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C91" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A91,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>1</v>
       </c>
@@ -4321,17 +4299,17 @@
         <v>2</v>
       </c>
       <c r="G91" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C92" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C92" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A92,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -4348,17 +4326,17 @@
         <v>0</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="6" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C93" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C93" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A93,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -4375,17 +4353,17 @@
         <v>0</v>
       </c>
       <c r="G93" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C94" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C94" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A94,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -4402,17 +4380,17 @@
         <v>0</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="6" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C95" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C95" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A95,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -4429,17 +4407,17 @@
         <v>0</v>
       </c>
       <c r="G95" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C96" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C96" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A96,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -4456,17 +4434,17 @@
         <v>0</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="6" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C97" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C97" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A97,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -4483,17 +4461,17 @@
         <v>0</v>
       </c>
       <c r="G97" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="6" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C98" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C98" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A98,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -4510,17 +4488,17 @@
         <v>0</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C99" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C99" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A99,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -4537,17 +4515,17 @@
         <v>0</v>
       </c>
       <c r="G99" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="6" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C100" s="10" t="b">
+        <v>58</v>
+      </c>
+      <c r="C100" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A100,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -4564,17 +4542,17 @@
         <v>0</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="6" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C101" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C101" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A101,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -4591,17 +4569,17 @@
         <v>0</v>
       </c>
       <c r="G101" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="6" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C102" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C102" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A102,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -4618,17 +4596,17 @@
         <v>0</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="6" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C103" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C103" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A103,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -4645,17 +4623,17 @@
         <v>0</v>
       </c>
       <c r="G103" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="6" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C104" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C104" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A104,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -4672,17 +4650,17 @@
         <v>0</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="6" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C105" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C105" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A105,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -4699,17 +4677,17 @@
         <v>0</v>
       </c>
       <c r="G105" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="6" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C106" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C106" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A106,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -4726,17 +4704,17 @@
         <v>0</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="6" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C107" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C107" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A107,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -4753,17 +4731,17 @@
         <v>0</v>
       </c>
       <c r="G107" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="6" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C108" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C108" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A108,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -4780,17 +4758,17 @@
         <v>0</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="6" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C109" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C109" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A109,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -4807,17 +4785,17 @@
         <v>0</v>
       </c>
       <c r="G109" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="6" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C110" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C110" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A110,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -4834,17 +4812,17 @@
         <v>0</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="6" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C111" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C111" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A111,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -4861,17 +4839,17 @@
         <v>0</v>
       </c>
       <c r="G111" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="6" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C112" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C112" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A112,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -4888,17 +4866,17 @@
         <v>0</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="6" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C113" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C113" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A113,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -4915,17 +4893,17 @@
         <v>0</v>
       </c>
       <c r="G113" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="6" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C114" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C114" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A114,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -4942,17 +4920,17 @@
         <v>0</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C115" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C115" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A115,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -4969,17 +4947,17 @@
         <v>0</v>
       </c>
       <c r="G115" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C116" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C116" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A116,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -4996,17 +4974,17 @@
         <v>0</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C117" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C117" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A117,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -5023,17 +5001,17 @@
         <v>0</v>
       </c>
       <c r="G117" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="6" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C118" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C118" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A118,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -5050,17 +5028,17 @@
         <v>0</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="6" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C119" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C119" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A119,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -5077,17 +5055,17 @@
         <v>0</v>
       </c>
       <c r="G119" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="6" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C120" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C120" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A120,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -5104,17 +5082,17 @@
         <v>0</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="6" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B121" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C121" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C121" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A121,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -5131,17 +5109,17 @@
         <v>0</v>
       </c>
       <c r="G121" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="6" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B122" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C122" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C122" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A122,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -5158,17 +5136,17 @@
         <v>0</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="6" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C123" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C123" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A123,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -5185,17 +5163,17 @@
         <v>0</v>
       </c>
       <c r="G123" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C124" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C124" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A124,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -5212,17 +5190,17 @@
         <v>0</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C125" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C125" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A125,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -5239,17 +5217,17 @@
         <v>0</v>
       </c>
       <c r="G125" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="6" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C126" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C126" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A126,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -5266,17 +5244,17 @@
         <v>0</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="6" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B127" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C127" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C127" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A127,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -5293,17 +5271,17 @@
         <v>0</v>
       </c>
       <c r="G127" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="6" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C128" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C128" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A128,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -5320,17 +5298,17 @@
         <v>0</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="6" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C129" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C129" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A129,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -5347,17 +5325,17 @@
         <v>0</v>
       </c>
       <c r="G129" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C130" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C130" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A130,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -5374,17 +5352,17 @@
         <v>0</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="6" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C131" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C131" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A131,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -5401,17 +5379,17 @@
         <v>0</v>
       </c>
       <c r="G131" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C132" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C132" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A132,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -5428,17 +5406,17 @@
         <v>0</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="6" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B133" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C133" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C133" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A133,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -5455,17 +5433,17 @@
         <v>0</v>
       </c>
       <c r="G133" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="6" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C134" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C134" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A134,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -5482,17 +5460,17 @@
         <v>0</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="6" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C135" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C135" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A135,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -5509,17 +5487,17 @@
         <v>0</v>
       </c>
       <c r="G135" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="6" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C136" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C136" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A136,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -5536,17 +5514,17 @@
         <v>0</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="6" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B137" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C137" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C137" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A137,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -5563,17 +5541,17 @@
         <v>0</v>
       </c>
       <c r="G137" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A138" s="6" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B138" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C138" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C138" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A138,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -5590,17 +5568,17 @@
         <v>0</v>
       </c>
       <c r="G138" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="6" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B139" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C139" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C139" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A139,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -5617,17 +5595,17 @@
         <v>0</v>
       </c>
       <c r="G139" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="6" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B140" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C140" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C140" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A140,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -5644,17 +5622,17 @@
         <v>0</v>
       </c>
       <c r="G140" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="6" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B141" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C141" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C141" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A141,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -5671,17 +5649,17 @@
         <v>0</v>
       </c>
       <c r="G141" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="6" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B142" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C142" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C142" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A142,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -5698,17 +5676,17 @@
         <v>0</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="6" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B143" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C143" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C143" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A143,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -5725,17 +5703,17 @@
         <v>0</v>
       </c>
       <c r="G143" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B144" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C144" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C144" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A144,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -5752,17 +5730,17 @@
         <v>0</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="6" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B145" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C145" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C145" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A145,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -5779,17 +5757,17 @@
         <v>0</v>
       </c>
       <c r="G145" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="6" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B146" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C146" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C146" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A146,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -5806,17 +5784,17 @@
         <v>0</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B147" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C147" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C147" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A147,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -5833,17 +5811,17 @@
         <v>0</v>
       </c>
       <c r="G147" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="6" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B148" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C148" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C148" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A148,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -5860,17 +5838,17 @@
         <v>0</v>
       </c>
       <c r="G148" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="6" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B149" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C149" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C149" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A149,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -5887,17 +5865,17 @@
         <v>0</v>
       </c>
       <c r="G149" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="6" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B150" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C150" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C150" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A150,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -5914,17 +5892,17 @@
         <v>0</v>
       </c>
       <c r="G150" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A151" s="6" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B151" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C151" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C151" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A151,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -5941,17 +5919,17 @@
         <v>0</v>
       </c>
       <c r="G151" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A152" s="6" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B152" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C152" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C152" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A152,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -5968,17 +5946,17 @@
         <v>0</v>
       </c>
       <c r="G152" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A153" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B153" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C153" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C153" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A153,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -5995,17 +5973,17 @@
         <v>0</v>
       </c>
       <c r="G153" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A154" s="6" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B154" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C154" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C154" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A154,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -6022,17 +6000,17 @@
         <v>0</v>
       </c>
       <c r="G154" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A155" s="6" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B155" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C155" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C155" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A155,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -6049,17 +6027,17 @@
         <v>0</v>
       </c>
       <c r="G155" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A156" s="6" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B156" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C156" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C156" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A156,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -6076,17 +6054,17 @@
         <v>0</v>
       </c>
       <c r="G156" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A157" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B157" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C157" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C157" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A157,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -6103,17 +6081,17 @@
         <v>0</v>
       </c>
       <c r="G157" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A158" s="6" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B158" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C158" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C158" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A158,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -6130,17 +6108,17 @@
         <v>0</v>
       </c>
       <c r="G158" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A159" s="6" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B159" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C159" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C159" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A159,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -6157,17 +6135,17 @@
         <v>0</v>
       </c>
       <c r="G159" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="6" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B160" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C160" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C160" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A160,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -6184,17 +6162,17 @@
         <v>0</v>
       </c>
       <c r="G160" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="6" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B161" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C161" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C161" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A161,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -6211,17 +6189,17 @@
         <v>0</v>
       </c>
       <c r="G161" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="6" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B162" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C162" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C162" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A162,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -6238,17 +6216,17 @@
         <v>0</v>
       </c>
       <c r="G162" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="6" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B163" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C163" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C163" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A163,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -6265,17 +6243,17 @@
         <v>0</v>
       </c>
       <c r="G163" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="6" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B164" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C164" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C164" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A164,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -6292,17 +6270,17 @@
         <v>0</v>
       </c>
       <c r="G164" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="6" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B165" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C165" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C165" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A165,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -6319,17 +6297,17 @@
         <v>0</v>
       </c>
       <c r="G165" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="6" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B166" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C166" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C166" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A166,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -6346,17 +6324,17 @@
         <v>0</v>
       </c>
       <c r="G166" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A167" s="6" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B167" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C167" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C167" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A167,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -6373,17 +6351,17 @@
         <v>0</v>
       </c>
       <c r="G167" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="6" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B168" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C168" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C168" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A168,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -6400,17 +6378,17 @@
         <v>0</v>
       </c>
       <c r="G168" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="6" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B169" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C169" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C169" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A169,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -6427,17 +6405,17 @@
         <v>0</v>
       </c>
       <c r="G169" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="6" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B170" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C170" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C170" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A170,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -6454,17 +6432,17 @@
         <v>0</v>
       </c>
       <c r="G170" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A171" s="6" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B171" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C171" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C171" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A171,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -6481,17 +6459,17 @@
         <v>0</v>
       </c>
       <c r="G171" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="6" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B172" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C172" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C172" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A172,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -6508,17 +6486,17 @@
         <v>0</v>
       </c>
       <c r="G172" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="6" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B173" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C173" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C173" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A173,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -6535,17 +6513,17 @@
         <v>0</v>
       </c>
       <c r="G173" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="6" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B174" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C174" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C174" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A174,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -6562,17 +6540,17 @@
         <v>0</v>
       </c>
       <c r="G174" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="6" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B175" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C175" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C175" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A175,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -6589,17 +6567,17 @@
         <v>0</v>
       </c>
       <c r="G175" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="6" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B176" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C176" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C176" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A176,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -6616,17 +6594,17 @@
         <v>0</v>
       </c>
       <c r="G176" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="6" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B177" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C177" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C177" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A177,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -6643,17 +6621,17 @@
         <v>0</v>
       </c>
       <c r="G177" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="6" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B178" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C178" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C178" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A178,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -6670,17 +6648,17 @@
         <v>0</v>
       </c>
       <c r="G178" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="6" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B179" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C179" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C179" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A179,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -6697,17 +6675,17 @@
         <v>0</v>
       </c>
       <c r="G179" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="6" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B180" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C180" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C180" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A180,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -6724,17 +6702,17 @@
         <v>0</v>
       </c>
       <c r="G180" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="6" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B181" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C181" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C181" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A181,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -6751,17 +6729,17 @@
         <v>0</v>
       </c>
       <c r="G181" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="6" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B182" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C182" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C182" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A182,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -6778,17 +6756,17 @@
         <v>0</v>
       </c>
       <c r="G182" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="6" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B183" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C183" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C183" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A183,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -6805,17 +6783,17 @@
         <v>0</v>
       </c>
       <c r="G183" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="6" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B184" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C184" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C184" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A184,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -6832,17 +6810,17 @@
         <v>0</v>
       </c>
       <c r="G184" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="6" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B185" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C185" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C185" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A185,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -6859,17 +6837,17 @@
         <v>0</v>
       </c>
       <c r="G185" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A186" s="6" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B186" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C186" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C186" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A186,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -6886,17 +6864,17 @@
         <v>0</v>
       </c>
       <c r="G186" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="6" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B187" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C187" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C187" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A187,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -6913,17 +6891,17 @@
         <v>0</v>
       </c>
       <c r="G187" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="6" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B188" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C188" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C188" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A188,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -6940,17 +6918,17 @@
         <v>0</v>
       </c>
       <c r="G188" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="6" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B189" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C189" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C189" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A189,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -6967,17 +6945,17 @@
         <v>0</v>
       </c>
       <c r="G189" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="6" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B190" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C190" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C190" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A190,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -6994,17 +6972,17 @@
         <v>0</v>
       </c>
       <c r="G190" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A191" s="6" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B191" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C191" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C191" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A191,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -7021,17 +6999,17 @@
         <v>0</v>
       </c>
       <c r="G191" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="6" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B192" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C192" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C192" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A192,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -7048,17 +7026,17 @@
         <v>0</v>
       </c>
       <c r="G192" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A193" s="6" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B193" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C193" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C193" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A193,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -7075,17 +7053,17 @@
         <v>0</v>
       </c>
       <c r="G193" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="6" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B194" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C194" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C194" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A194,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -7102,17 +7080,17 @@
         <v>0</v>
       </c>
       <c r="G194" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A195" s="6" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B195" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C195" s="10" t="b">
+        <v>156</v>
+      </c>
+      <c r="C195" s="6" t="b">
         <f aca="false">--ISNUMBER(SEARCH(A195,LOWER(Inputs!$B$5&amp;" "&amp;Inputs!$B$6)))</f>
         <v>0</v>
       </c>
@@ -7129,7 +7107,7 @@
         <v>0</v>
       </c>
       <c r="G195" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7143,7 +7121,7 @@
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A197" s="5" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B197" s="5"/>
       <c r="C197" s="5" t="n">
@@ -7202,7 +7180,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -7229,32 +7207,32 @@
       <c r="K2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11" t="s">
-        <v>255</v>
-      </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11"/>
-      <c r="J3" s="11"/>
-      <c r="K3" s="11"/>
+      <c r="A3" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="12"/>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
-      <c r="J4" s="12"/>
-      <c r="K4" s="12"/>
+      <c r="A4" s="11"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="11"/>
+      <c r="K4" s="11"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4"/>
@@ -7271,42 +7249,42 @@
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>256</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="D6" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="E6" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="F6" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="G6" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="H6" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="I6" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="J6" s="5" t="s">
         <v>263</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="K6" s="5" t="s">
         <v>264</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="K6" s="5" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B7" s="6" t="n">
         <f aca="false">'Keyword Influence'!D197</f>
@@ -7319,7 +7297,7 @@
         <f aca="false">(C7+'Model Parameters'!$B$11)/('Model Parameters'!$B$9+'Model Parameters'!$B$11*'Model Parameters'!$B$10)</f>
         <v>0.409825410909202</v>
       </c>
-      <c r="E7" s="13" t="n">
+      <c r="E7" s="12" t="n">
         <f aca="false">B7*LN(D7)</f>
         <v>-28.544769184787</v>
       </c>
@@ -7330,7 +7308,7 @@
         <f aca="false">(F7+'Model Parameters'!$C$11)/('Model Parameters'!$C$9+'Model Parameters'!$C$11*'Model Parameters'!$C$10)</f>
         <v>0.0397601820522396</v>
       </c>
-      <c r="H7" s="13" t="n">
+      <c r="H7" s="12" t="n">
         <f aca="false">B7*LN(G7)</f>
         <v>-103.196458189619</v>
       </c>
@@ -7341,14 +7319,14 @@
         <f aca="false">(I7+'Model Parameters'!$D$11)/('Model Parameters'!$D$9+'Model Parameters'!$D$11*'Model Parameters'!$D$10)</f>
         <v>0.196408732607967</v>
       </c>
-      <c r="K7" s="13" t="n">
+      <c r="K7" s="12" t="n">
         <f aca="false">B7*LN(J7)</f>
         <v>-52.0818374614256</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B8" s="6" t="n">
         <f aca="false">'Keyword Influence'!F197</f>
@@ -7361,7 +7339,7 @@
         <f aca="false">(C8+'Model Parameters'!$B$11)/('Model Parameters'!$B$9+'Model Parameters'!$B$11*'Model Parameters'!$B$10)</f>
         <v>0.413628038380166</v>
       </c>
-      <c r="E8" s="13" t="n">
+      <c r="E8" s="12" t="n">
         <f aca="false">B8*LN(D8)</f>
         <v>-28.2492213449942</v>
       </c>
@@ -7372,7 +7350,7 @@
         <f aca="false">(F8+'Model Parameters'!$C$11)/('Model Parameters'!$C$9+'Model Parameters'!$C$11*'Model Parameters'!$C$10)</f>
         <v>0.38999863483385</v>
       </c>
-      <c r="H8" s="13" t="n">
+      <c r="H8" s="12" t="n">
         <f aca="false">B8*LN(G8)</f>
         <v>-30.1315852892991</v>
       </c>
@@ -7383,14 +7361,14 @@
         <f aca="false">(I8+'Model Parameters'!$D$11)/('Model Parameters'!$D$9+'Model Parameters'!$D$11*'Model Parameters'!$D$10)</f>
         <v>0.196408732607967</v>
       </c>
-      <c r="K8" s="13" t="n">
+      <c r="K8" s="12" t="n">
         <f aca="false">B8*LN(J8)</f>
         <v>-52.0818374614256</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B9" s="6" t="n">
         <v>3</v>
@@ -7402,7 +7380,7 @@
         <f aca="false">(C9+'Model Parameters'!$B$11)/('Model Parameters'!$B$9+'Model Parameters'!$B$11*'Model Parameters'!$B$10)</f>
         <v>0.00478263347690308</v>
       </c>
-      <c r="E9" s="13" t="n">
+      <c r="E9" s="12" t="n">
         <f aca="false">B9*LN(D9)</f>
         <v>-16.028291842794</v>
       </c>
@@ -7413,7 +7391,7 @@
         <f aca="false">(F9+'Model Parameters'!$C$11)/('Model Parameters'!$C$9+'Model Parameters'!$C$11*'Model Parameters'!$C$10)</f>
         <v>4.5129459495746E-005</v>
       </c>
-      <c r="H9" s="13" t="n">
+      <c r="H9" s="12" t="n">
         <f aca="false">B9*LN(G9)</f>
         <v>-30.0179259624109</v>
       </c>
@@ -7424,14 +7402,14 @@
         <f aca="false">(I9+'Model Parameters'!$D$11)/('Model Parameters'!$D$9+'Model Parameters'!$D$11*'Model Parameters'!$D$10)</f>
         <v>0.00679369390022396</v>
       </c>
-      <c r="K9" s="13" t="n">
+      <c r="K9" s="12" t="n">
         <f aca="false">B9*LN(J9)</f>
         <v>-14.9752813940567</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B10" s="6" t="n">
         <v>3</v>
@@ -7443,7 +7421,7 @@
         <f aca="false">(C10+'Model Parameters'!$B$11)/('Model Parameters'!$B$9+'Model Parameters'!$B$11*'Model Parameters'!$B$10)</f>
         <v>0.00304380337608666</v>
       </c>
-      <c r="E10" s="13" t="n">
+      <c r="E10" s="12" t="n">
         <f aca="false">B10*LN(D10)</f>
         <v>-17.3839423049875</v>
       </c>
@@ -7454,7 +7432,7 @@
         <f aca="false">(F10+'Model Parameters'!$C$11)/('Model Parameters'!$C$9+'Model Parameters'!$C$11*'Model Parameters'!$C$10)</f>
         <v>3.38470946218095E-005</v>
       </c>
-      <c r="H10" s="13" t="n">
+      <c r="H10" s="12" t="n">
         <f aca="false">B10*LN(G10)</f>
         <v>-30.8809721797663</v>
       </c>
@@ -7465,14 +7443,14 @@
         <f aca="false">(I10+'Model Parameters'!$D$11)/('Model Parameters'!$D$9+'Model Parameters'!$D$11*'Model Parameters'!$D$10)</f>
         <v>8.8172536018481E-006</v>
       </c>
-      <c r="K10" s="13" t="n">
+      <c r="K10" s="12" t="n">
         <f aca="false">B10*LN(J10)</f>
         <v>-34.9164003583373</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B11" s="6" t="n">
         <v>2</v>
@@ -7484,7 +7462,7 @@
         <f aca="false">(C11+'Model Parameters'!$B$11)/('Model Parameters'!$B$9+'Model Parameters'!$B$11*'Model Parameters'!$B$10)</f>
         <v>0.000406634436492293</v>
       </c>
-      <c r="E11" s="13" t="n">
+      <c r="E11" s="12" t="n">
         <f aca="false">B11*LN(D11)</f>
         <v>-15.6151919331461</v>
       </c>
@@ -7495,7 +7473,7 @@
         <f aca="false">(F11+'Model Parameters'!$C$11)/('Model Parameters'!$C$9+'Model Parameters'!$C$11*'Model Parameters'!$C$10)</f>
         <v>6.7694189243619E-006</v>
       </c>
-      <c r="H11" s="13" t="n">
+      <c r="H11" s="12" t="n">
         <f aca="false">B11*LN(G11)</f>
         <v>-23.8061906113791</v>
       </c>
@@ -7506,14 +7484,14 @@
         <f aca="false">(I11+'Model Parameters'!$D$11)/('Model Parameters'!$D$9+'Model Parameters'!$D$11*'Model Parameters'!$D$10)</f>
         <v>8.8172536018481E-006</v>
       </c>
-      <c r="K11" s="13" t="n">
+      <c r="K11" s="12" t="n">
         <f aca="false">B11*LN(J11)</f>
         <v>-23.2776002388915</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B12" s="6" t="n">
         <v>2</v>
@@ -7525,7 +7503,7 @@
         <f aca="false">(C12+'Model Parameters'!$B$11)/('Model Parameters'!$B$9+'Model Parameters'!$B$11*'Model Parameters'!$B$10)</f>
         <v>0.000710334214374612</v>
       </c>
-      <c r="E12" s="13" t="n">
+      <c r="E12" s="12" t="n">
         <f aca="false">B12*LN(D12)</f>
         <v>-14.4995499484273</v>
       </c>
@@ -7536,7 +7514,7 @@
         <f aca="false">(F12+'Model Parameters'!$C$11)/('Model Parameters'!$C$9+'Model Parameters'!$C$11*'Model Parameters'!$C$10)</f>
         <v>0.000469346378755758</v>
       </c>
-      <c r="H12" s="13" t="n">
+      <c r="H12" s="12" t="n">
         <f aca="false">B12*LN(G12)</f>
         <v>-15.3283390293126</v>
       </c>
@@ -7547,14 +7525,14 @@
         <f aca="false">(I12+'Model Parameters'!$D$11)/('Model Parameters'!$D$9+'Model Parameters'!$D$11*'Model Parameters'!$D$10)</f>
         <v>4.40862680092405E-006</v>
       </c>
-      <c r="K12" s="13" t="n">
+      <c r="K12" s="12" t="n">
         <f aca="false">B12*LN(J12)</f>
         <v>-24.6638946000114</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B13" s="6" t="n">
         <v>2</v>
@@ -7566,7 +7544,7 @@
         <f aca="false">(C13+'Model Parameters'!$B$11)/('Model Parameters'!$B$9+'Model Parameters'!$B$11*'Model Parameters'!$B$10)</f>
         <v>0.00117821902623813</v>
       </c>
-      <c r="E13" s="13" t="n">
+      <c r="E13" s="12" t="n">
         <f aca="false">B13*LN(D13)</f>
         <v>-13.4875025608861</v>
       </c>
@@ -7577,7 +7555,7 @@
         <f aca="false">(F13+'Model Parameters'!$C$11)/('Model Parameters'!$C$9+'Model Parameters'!$C$11*'Model Parameters'!$C$10)</f>
         <v>1.12823648739365E-006</v>
       </c>
-      <c r="H13" s="13" t="n">
+      <c r="H13" s="12" t="n">
         <f aca="false">B13*LN(G13)</f>
         <v>-27.3897095498352</v>
       </c>
@@ -7588,14 +7566,14 @@
         <f aca="false">(I13+'Model Parameters'!$D$11)/('Model Parameters'!$D$9+'Model Parameters'!$D$11*'Model Parameters'!$D$10)</f>
         <v>4.40862680092405E-006</v>
       </c>
-      <c r="K13" s="13" t="n">
+      <c r="K13" s="12" t="n">
         <f aca="false">B13*LN(J13)</f>
         <v>-24.6638946000114</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B14" s="6" t="n">
         <v>2</v>
@@ -7607,7 +7585,7 @@
         <f aca="false">(C14+'Model Parameters'!$B$11)/('Model Parameters'!$B$9+'Model Parameters'!$B$11*'Model Parameters'!$B$10)</f>
         <v>0.00160101675623116</v>
       </c>
-      <c r="E14" s="13" t="n">
+      <c r="E14" s="12" t="n">
         <f aca="false">B14*LN(D14)</f>
         <v>-12.8742327578383</v>
       </c>
@@ -7618,7 +7596,7 @@
         <f aca="false">(F14+'Model Parameters'!$C$11)/('Model Parameters'!$C$9+'Model Parameters'!$C$11*'Model Parameters'!$C$10)</f>
         <v>2.14364932604793E-005</v>
       </c>
-      <c r="H14" s="13" t="n">
+      <c r="H14" s="12" t="n">
         <f aca="false">B14*LN(G14)</f>
         <v>-21.5008315915023</v>
       </c>
@@ -7629,14 +7607,14 @@
         <f aca="false">(I14+'Model Parameters'!$D$11)/('Model Parameters'!$D$9+'Model Parameters'!$D$11*'Model Parameters'!$D$10)</f>
         <v>9.2581162819405E-005</v>
       </c>
-      <c r="K14" s="13" t="n">
+      <c r="K14" s="12" t="n">
         <f aca="false">B14*LN(J14)</f>
         <v>-18.5748497245645</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B15" s="6" t="n">
         <v>2</v>
@@ -7648,7 +7626,7 @@
         <f aca="false">(C15+'Model Parameters'!$B$11)/('Model Parameters'!$B$9+'Model Parameters'!$B$11*'Model Parameters'!$B$10)</f>
         <v>0.000386217644701885</v>
       </c>
-      <c r="E15" s="13" t="n">
+      <c r="E15" s="12" t="n">
         <f aca="false">B15*LN(D15)</f>
         <v>-15.7182190020463</v>
       </c>
@@ -7659,7 +7637,7 @@
         <f aca="false">(F15+'Model Parameters'!$C$11)/('Model Parameters'!$C$9+'Model Parameters'!$C$11*'Model Parameters'!$C$10)</f>
         <v>1.12823648739365E-006</v>
       </c>
-      <c r="H15" s="13" t="n">
+      <c r="H15" s="12" t="n">
         <f aca="false">B15*LN(G15)</f>
         <v>-27.3897095498352</v>
       </c>
@@ -7670,14 +7648,14 @@
         <f aca="false">(I15+'Model Parameters'!$D$11)/('Model Parameters'!$D$9+'Model Parameters'!$D$11*'Model Parameters'!$D$10)</f>
         <v>4.40862680092405E-006</v>
       </c>
-      <c r="K15" s="13" t="n">
+      <c r="K15" s="12" t="n">
         <f aca="false">B15*LN(J15)</f>
         <v>-24.6638946000114</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B16" s="6" t="n">
         <v>2</v>
@@ -7689,7 +7667,7 @@
         <f aca="false">(C16+'Model Parameters'!$B$11)/('Model Parameters'!$B$9+'Model Parameters'!$B$11*'Model Parameters'!$B$10)</f>
         <v>0.000425349828966834</v>
       </c>
-      <c r="E16" s="13" t="n">
+      <c r="E16" s="12" t="n">
         <f aca="false">B16*LN(D16)</f>
         <v>-15.5251972012846</v>
       </c>
@@ -7700,7 +7678,7 @@
         <f aca="false">(F16+'Model Parameters'!$C$11)/('Model Parameters'!$C$9+'Model Parameters'!$C$11*'Model Parameters'!$C$10)</f>
         <v>6.7694189243619E-006</v>
       </c>
-      <c r="H16" s="13" t="n">
+      <c r="H16" s="12" t="n">
         <f aca="false">B16*LN(G16)</f>
         <v>-23.8061906113791</v>
       </c>
@@ -7711,14 +7689,14 @@
         <f aca="false">(I16+'Model Parameters'!$D$11)/('Model Parameters'!$D$9+'Model Parameters'!$D$11*'Model Parameters'!$D$10)</f>
         <v>4.40862680092405E-006</v>
       </c>
-      <c r="K16" s="13" t="n">
+      <c r="K16" s="12" t="n">
         <f aca="false">B16*LN(J16)</f>
         <v>-24.6638946000114</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B17" s="6" t="n">
         <v>2</v>
@@ -7730,7 +7708,7 @@
         <f aca="false">(C17+'Model Parameters'!$B$11)/('Model Parameters'!$B$9+'Model Parameters'!$B$11*'Model Parameters'!$B$10)</f>
         <v>0.000387068344359819</v>
       </c>
-      <c r="E17" s="13" t="n">
+      <c r="E17" s="12" t="n">
         <f aca="false">B17*LN(D17)</f>
         <v>-15.7138185602271</v>
       </c>
@@ -7741,7 +7719,7 @@
         <f aca="false">(F17+'Model Parameters'!$C$11)/('Model Parameters'!$C$9+'Model Parameters'!$C$11*'Model Parameters'!$C$10)</f>
         <v>1.12823648739365E-006</v>
       </c>
-      <c r="H17" s="13" t="n">
+      <c r="H17" s="12" t="n">
         <f aca="false">B17*LN(G17)</f>
         <v>-27.3897095498352</v>
       </c>
@@ -7752,14 +7730,14 @@
         <f aca="false">(I17+'Model Parameters'!$D$11)/('Model Parameters'!$D$9+'Model Parameters'!$D$11*'Model Parameters'!$D$10)</f>
         <v>4.40862680092405E-006</v>
       </c>
-      <c r="K17" s="13" t="n">
+      <c r="K17" s="12" t="n">
         <f aca="false">B17*LN(J17)</f>
         <v>-24.6638946000114</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B18" s="6" t="n">
         <v>1</v>
@@ -7771,7 +7749,7 @@
         <f aca="false">(C18+'Model Parameters'!$B$11)/('Model Parameters'!$B$9+'Model Parameters'!$B$11*'Model Parameters'!$B$10)</f>
         <v>3.40279863173467E-006</v>
       </c>
-      <c r="E18" s="13" t="n">
+      <c r="E18" s="12" t="n">
         <f aca="false">B18*LN(D18)</f>
         <v>-12.5909123379446</v>
       </c>
@@ -7782,7 +7760,7 @@
         <f aca="false">(F18+'Model Parameters'!$C$11)/('Model Parameters'!$C$9+'Model Parameters'!$C$11*'Model Parameters'!$C$10)</f>
         <v>1.12823648739365E-006</v>
       </c>
-      <c r="H18" s="13" t="n">
+      <c r="H18" s="12" t="n">
         <f aca="false">B18*LN(G18)</f>
         <v>-13.6948547749176</v>
       </c>
@@ -7793,14 +7771,14 @@
         <f aca="false">(I18+'Model Parameters'!$D$11)/('Model Parameters'!$D$9+'Model Parameters'!$D$11*'Model Parameters'!$D$10)</f>
         <v>4.40862680092405E-006</v>
       </c>
-      <c r="K18" s="13" t="n">
+      <c r="K18" s="12" t="n">
         <f aca="false">B18*LN(J18)</f>
         <v>-12.3319473000057</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B19" s="6" t="n">
         <v>1</v>
@@ -7812,7 +7790,7 @@
         <f aca="false">(C19+'Model Parameters'!$B$11)/('Model Parameters'!$B$9+'Model Parameters'!$B$11*'Model Parameters'!$B$10)</f>
         <v>0.000262866194301503</v>
       </c>
-      <c r="E19" s="13" t="n">
+      <c r="E19" s="12" t="n">
         <f aca="false">B19*LN(D19)</f>
         <v>-8.24386542216675</v>
       </c>
@@ -7823,7 +7801,7 @@
         <f aca="false">(F19+'Model Parameters'!$C$11)/('Model Parameters'!$C$9+'Model Parameters'!$C$11*'Model Parameters'!$C$10)</f>
         <v>1.12823648739365E-006</v>
       </c>
-      <c r="H19" s="13" t="n">
+      <c r="H19" s="12" t="n">
         <f aca="false">B19*LN(G19)</f>
         <v>-13.6948547749176</v>
       </c>
@@ -7834,14 +7812,14 @@
         <f aca="false">(I19+'Model Parameters'!$D$11)/('Model Parameters'!$D$9+'Model Parameters'!$D$11*'Model Parameters'!$D$10)</f>
         <v>4.40862680092405E-006</v>
       </c>
-      <c r="K19" s="13" t="n">
+      <c r="K19" s="12" t="n">
         <f aca="false">B19*LN(J19)</f>
         <v>-12.3319473000057</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B20" s="6" t="n">
         <v>1</v>
@@ -7853,7 +7831,7 @@
         <f aca="false">(C20+'Model Parameters'!$B$11)/('Model Parameters'!$B$9+'Model Parameters'!$B$11*'Model Parameters'!$B$10)</f>
         <v>1.61632935007397E-005</v>
       </c>
-      <c r="E20" s="13" t="n">
+      <c r="E20" s="12" t="n">
         <f aca="false">B20*LN(D20)</f>
         <v>-11.0327677198981</v>
       </c>
@@ -7864,7 +7842,7 @@
         <f aca="false">(F20+'Model Parameters'!$C$11)/('Model Parameters'!$C$9+'Model Parameters'!$C$11*'Model Parameters'!$C$10)</f>
         <v>1.12823648739365E-006</v>
       </c>
-      <c r="H20" s="13" t="n">
+      <c r="H20" s="12" t="n">
         <f aca="false">B20*LN(G20)</f>
         <v>-13.6948547749176</v>
       </c>
@@ -7875,14 +7853,14 @@
         <f aca="false">(I20+'Model Parameters'!$D$11)/('Model Parameters'!$D$9+'Model Parameters'!$D$11*'Model Parameters'!$D$10)</f>
         <v>4.40862680092405E-006</v>
       </c>
-      <c r="K20" s="13" t="n">
+      <c r="K20" s="12" t="n">
         <f aca="false">B20*LN(J20)</f>
         <v>-12.3319473000057</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B21" s="6" t="n">
         <v>1</v>
@@ -7894,7 +7872,7 @@
         <f aca="false">(C21+'Model Parameters'!$B$11)/('Model Parameters'!$B$9+'Model Parameters'!$B$11*'Model Parameters'!$B$10)</f>
         <v>0.00102424238815214</v>
       </c>
-      <c r="E21" s="13" t="n">
+      <c r="E21" s="12" t="n">
         <f aca="false">B21*LN(D21)</f>
         <v>-6.88380207319573</v>
       </c>
@@ -7905,7 +7883,7 @@
         <f aca="false">(F21+'Model Parameters'!$C$11)/('Model Parameters'!$C$9+'Model Parameters'!$C$11*'Model Parameters'!$C$10)</f>
         <v>1.12823648739365E-006</v>
       </c>
-      <c r="H21" s="13" t="n">
+      <c r="H21" s="12" t="n">
         <f aca="false">B21*LN(G21)</f>
         <v>-13.6948547749176</v>
       </c>
@@ -7916,14 +7894,14 @@
         <f aca="false">(I21+'Model Parameters'!$D$11)/('Model Parameters'!$D$9+'Model Parameters'!$D$11*'Model Parameters'!$D$10)</f>
         <v>4.40862680092405E-006</v>
       </c>
-      <c r="K21" s="13" t="n">
+      <c r="K21" s="12" t="n">
         <f aca="false">B21*LN(J21)</f>
         <v>-12.3319473000057</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B22" s="6" t="n">
         <v>1</v>
@@ -7935,7 +7913,7 @@
         <f aca="false">(C22+'Model Parameters'!$B$11)/('Model Parameters'!$B$9+'Model Parameters'!$B$11*'Model Parameters'!$B$10)</f>
         <v>0.000789449282562444</v>
       </c>
-      <c r="E22" s="13" t="n">
+      <c r="E22" s="12" t="n">
         <f aca="false">B22*LN(D22)</f>
         <v>-7.14417496627829</v>
       </c>
@@ -7946,7 +7924,7 @@
         <f aca="false">(F22+'Model Parameters'!$C$11)/('Model Parameters'!$C$9+'Model Parameters'!$C$11*'Model Parameters'!$C$10)</f>
         <v>1.12823648739365E-006</v>
       </c>
-      <c r="H22" s="13" t="n">
+      <c r="H22" s="12" t="n">
         <f aca="false">B22*LN(G22)</f>
         <v>-13.6948547749176</v>
       </c>
@@ -7957,14 +7935,14 @@
         <f aca="false">(I22+'Model Parameters'!$D$11)/('Model Parameters'!$D$9+'Model Parameters'!$D$11*'Model Parameters'!$D$10)</f>
         <v>4.40862680092405E-006</v>
       </c>
-      <c r="K22" s="13" t="n">
+      <c r="K22" s="12" t="n">
         <f aca="false">B22*LN(J22)</f>
         <v>-12.3319473000057</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B23" s="6" t="n">
         <v>1</v>
@@ -7976,7 +7954,7 @@
         <f aca="false">(C23+'Model Parameters'!$B$11)/('Model Parameters'!$B$9+'Model Parameters'!$B$11*'Model Parameters'!$B$10)</f>
         <v>0.00089068254185655</v>
       </c>
-      <c r="E23" s="13" t="n">
+      <c r="E23" s="12" t="n">
         <f aca="false">B23*LN(D23)</f>
         <v>-7.02352248819395</v>
       </c>
@@ -7987,7 +7965,7 @@
         <f aca="false">(F23+'Model Parameters'!$C$11)/('Model Parameters'!$C$9+'Model Parameters'!$C$11*'Model Parameters'!$C$10)</f>
         <v>1.12823648739365E-006</v>
       </c>
-      <c r="H23" s="13" t="n">
+      <c r="H23" s="12" t="n">
         <f aca="false">B23*LN(G23)</f>
         <v>-13.6948547749176</v>
       </c>
@@ -7998,14 +7976,14 @@
         <f aca="false">(I23+'Model Parameters'!$D$11)/('Model Parameters'!$D$9+'Model Parameters'!$D$11*'Model Parameters'!$D$10)</f>
         <v>8.8172536018481E-006</v>
       </c>
-      <c r="K23" s="13" t="n">
+      <c r="K23" s="12" t="n">
         <f aca="false">B23*LN(J23)</f>
         <v>-11.6388001194457</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B24" s="6" t="n">
         <v>1</v>
@@ -8017,7 +7995,7 @@
         <f aca="false">(C24+'Model Parameters'!$B$11)/('Model Parameters'!$B$9+'Model Parameters'!$B$11*'Model Parameters'!$B$10)</f>
         <v>1.61632935007397E-005</v>
       </c>
-      <c r="E24" s="13" t="n">
+      <c r="E24" s="12" t="n">
         <f aca="false">B24*LN(D24)</f>
         <v>-11.0327677198981</v>
       </c>
@@ -8028,7 +8006,7 @@
         <f aca="false">(F24+'Model Parameters'!$C$11)/('Model Parameters'!$C$9+'Model Parameters'!$C$11*'Model Parameters'!$C$10)</f>
         <v>1.12823648739365E-006</v>
       </c>
-      <c r="H24" s="13" t="n">
+      <c r="H24" s="12" t="n">
         <f aca="false">B24*LN(G24)</f>
         <v>-13.6948547749176</v>
       </c>
@@ -8039,14 +8017,14 @@
         <f aca="false">(I24+'Model Parameters'!$D$11)/('Model Parameters'!$D$9+'Model Parameters'!$D$11*'Model Parameters'!$D$10)</f>
         <v>4.40862680092405E-006</v>
       </c>
-      <c r="K24" s="13" t="n">
+      <c r="K24" s="12" t="n">
         <f aca="false">B24*LN(J24)</f>
         <v>-12.3319473000057</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B25" s="6" t="n">
         <v>1</v>
@@ -8058,7 +8036,7 @@
         <f aca="false">(C25+'Model Parameters'!$B$11)/('Model Parameters'!$B$9+'Model Parameters'!$B$11*'Model Parameters'!$B$10)</f>
         <v>8.50699657933668E-007</v>
       </c>
-      <c r="E25" s="13" t="n">
+      <c r="E25" s="12" t="n">
         <f aca="false">B25*LN(D25)</f>
         <v>-13.9772066990645</v>
       </c>
@@ -8069,7 +8047,7 @@
         <f aca="false">(F25+'Model Parameters'!$C$11)/('Model Parameters'!$C$9+'Model Parameters'!$C$11*'Model Parameters'!$C$10)</f>
         <v>1.12823648739365E-006</v>
       </c>
-      <c r="H25" s="13" t="n">
+      <c r="H25" s="12" t="n">
         <f aca="false">B25*LN(G25)</f>
         <v>-13.6948547749176</v>
       </c>
@@ -8080,14 +8058,14 @@
         <f aca="false">(I25+'Model Parameters'!$D$11)/('Model Parameters'!$D$9+'Model Parameters'!$D$11*'Model Parameters'!$D$10)</f>
         <v>4.40862680092405E-006</v>
       </c>
-      <c r="K25" s="13" t="n">
+      <c r="K25" s="12" t="n">
         <f aca="false">B25*LN(J25)</f>
         <v>-12.3319473000057</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B26" s="6" t="n">
         <v>1</v>
@@ -8099,7 +8077,7 @@
         <f aca="false">(C26+'Model Parameters'!$B$11)/('Model Parameters'!$B$9+'Model Parameters'!$B$11*'Model Parameters'!$B$10)</f>
         <v>8.50699657933668E-007</v>
       </c>
-      <c r="E26" s="13" t="n">
+      <c r="E26" s="12" t="n">
         <f aca="false">B26*LN(D26)</f>
         <v>-13.9772066990645</v>
       </c>
@@ -8110,7 +8088,7 @@
         <f aca="false">(F26+'Model Parameters'!$C$11)/('Model Parameters'!$C$9+'Model Parameters'!$C$11*'Model Parameters'!$C$10)</f>
         <v>1.12823648739365E-006</v>
       </c>
-      <c r="H26" s="13" t="n">
+      <c r="H26" s="12" t="n">
         <f aca="false">B26*LN(G26)</f>
         <v>-13.6948547749176</v>
       </c>
@@ -8121,14 +8099,14 @@
         <f aca="false">(I26+'Model Parameters'!$D$11)/('Model Parameters'!$D$9+'Model Parameters'!$D$11*'Model Parameters'!$D$10)</f>
         <v>4.40862680092405E-006</v>
       </c>
-      <c r="K26" s="13" t="n">
+      <c r="K26" s="12" t="n">
         <f aca="false">B26*LN(J26)</f>
         <v>-12.3319473000057</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B27" s="6" t="n">
         <v>1</v>
@@ -8140,7 +8118,7 @@
         <f aca="false">(C27+'Model Parameters'!$B$11)/('Model Parameters'!$B$9+'Model Parameters'!$B$11*'Model Parameters'!$B$10)</f>
         <v>0.00140280373593262</v>
       </c>
-      <c r="E27" s="13" t="n">
+      <c r="E27" s="12" t="n">
         <f aca="false">B27*LN(D27)</f>
         <v>-6.56928237650489</v>
       </c>
@@ -8151,7 +8129,7 @@
         <f aca="false">(F27+'Model Parameters'!$C$11)/('Model Parameters'!$C$9+'Model Parameters'!$C$11*'Model Parameters'!$C$10)</f>
         <v>1.12823648739365E-005</v>
       </c>
-      <c r="H27" s="13" t="n">
+      <c r="H27" s="12" t="n">
         <f aca="false">B27*LN(G27)</f>
         <v>-11.3922696819235</v>
       </c>
@@ -8162,14 +8140,14 @@
         <f aca="false">(I27+'Model Parameters'!$D$11)/('Model Parameters'!$D$9+'Model Parameters'!$D$11*'Model Parameters'!$D$10)</f>
         <v>0.000626025005731215</v>
       </c>
-      <c r="K27" s="13" t="n">
+      <c r="K27" s="12" t="n">
         <f aca="false">B27*LN(J27)</f>
         <v>-7.37612024240443</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B28" s="6" t="n">
         <v>1</v>
@@ -8181,7 +8159,7 @@
         <f aca="false">(C28+'Model Parameters'!$B$11)/('Model Parameters'!$B$9+'Model Parameters'!$B$11*'Model Parameters'!$B$10)</f>
         <v>0.000731601705822954</v>
       </c>
-      <c r="E28" s="13" t="n">
+      <c r="E28" s="12" t="n">
         <f aca="false">B28*LN(D28)</f>
         <v>-7.22027430981694</v>
       </c>
@@ -8192,7 +8170,7 @@
         <f aca="false">(F28+'Model Parameters'!$C$11)/('Model Parameters'!$C$9+'Model Parameters'!$C$11*'Model Parameters'!$C$10)</f>
         <v>1.12823648739365E-006</v>
       </c>
-      <c r="H28" s="13" t="n">
+      <c r="H28" s="12" t="n">
         <f aca="false">B28*LN(G28)</f>
         <v>-13.6948547749176</v>
       </c>
@@ -8203,14 +8181,14 @@
         <f aca="false">(I28+'Model Parameters'!$D$11)/('Model Parameters'!$D$9+'Model Parameters'!$D$11*'Model Parameters'!$D$10)</f>
         <v>4.40862680092405E-006</v>
       </c>
-      <c r="K28" s="13" t="n">
+      <c r="K28" s="12" t="n">
         <f aca="false">B28*LN(J28)</f>
         <v>-12.3319473000057</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B29" s="6" t="n">
         <v>1</v>
@@ -8222,7 +8200,7 @@
         <f aca="false">(C29+'Model Parameters'!$B$11)/('Model Parameters'!$B$9+'Model Parameters'!$B$11*'Model Parameters'!$B$10)</f>
         <v>0.000866012251776474</v>
       </c>
-      <c r="E29" s="13" t="n">
+      <c r="E29" s="12" t="n">
         <f aca="false">B29*LN(D29)</f>
         <v>-7.05161150195402</v>
       </c>
@@ -8233,7 +8211,7 @@
         <f aca="false">(F29+'Model Parameters'!$C$11)/('Model Parameters'!$C$9+'Model Parameters'!$C$11*'Model Parameters'!$C$10)</f>
         <v>6.7694189243619E-006</v>
       </c>
-      <c r="H29" s="13" t="n">
+      <c r="H29" s="12" t="n">
         <f aca="false">B29*LN(G29)</f>
         <v>-11.9030953056895</v>
       </c>
@@ -8244,14 +8222,14 @@
         <f aca="false">(I29+'Model Parameters'!$D$11)/('Model Parameters'!$D$9+'Model Parameters'!$D$11*'Model Parameters'!$D$10)</f>
         <v>4.40862680092405E-006</v>
       </c>
-      <c r="K29" s="13" t="n">
+      <c r="K29" s="12" t="n">
         <f aca="false">B29*LN(J29)</f>
         <v>-12.3319473000057</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B30" s="6" t="n">
         <v>1</v>
@@ -8263,7 +8241,7 @@
         <f aca="false">(C30+'Model Parameters'!$B$11)/('Model Parameters'!$B$9+'Model Parameters'!$B$11*'Model Parameters'!$B$10)</f>
         <v>0.000822626569221857</v>
       </c>
-      <c r="E30" s="13" t="n">
+      <c r="E30" s="12" t="n">
         <f aca="false">B30*LN(D30)</f>
         <v>-7.1030082036112</v>
       </c>
@@ -8274,7 +8252,7 @@
         <f aca="false">(F30+'Model Parameters'!$C$11)/('Model Parameters'!$C$9+'Model Parameters'!$C$11*'Model Parameters'!$C$10)</f>
         <v>1.12823648739365E-006</v>
       </c>
-      <c r="H30" s="13" t="n">
+      <c r="H30" s="12" t="n">
         <f aca="false">B30*LN(G30)</f>
         <v>-13.6948547749176</v>
       </c>
@@ -8285,14 +8263,14 @@
         <f aca="false">(I30+'Model Parameters'!$D$11)/('Model Parameters'!$D$9+'Model Parameters'!$D$11*'Model Parameters'!$D$10)</f>
         <v>4.40862680092405E-006</v>
       </c>
-      <c r="K30" s="13" t="n">
+      <c r="K30" s="12" t="n">
         <f aca="false">B30*LN(J30)</f>
         <v>-12.3319473000057</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B31" s="6" t="n">
         <v>1</v>
@@ -8304,7 +8282,7 @@
         <f aca="false">(C31+'Model Parameters'!$B$11)/('Model Parameters'!$B$9+'Model Parameters'!$B$11*'Model Parameters'!$B$10)</f>
         <v>0.000262866194301503</v>
       </c>
-      <c r="E31" s="13" t="n">
+      <c r="E31" s="12" t="n">
         <f aca="false">B31*LN(D31)</f>
         <v>-8.24386542216675</v>
       </c>
@@ -8315,7 +8293,7 @@
         <f aca="false">(F31+'Model Parameters'!$C$11)/('Model Parameters'!$C$9+'Model Parameters'!$C$11*'Model Parameters'!$C$10)</f>
         <v>1.12823648739365E-006</v>
       </c>
-      <c r="H31" s="13" t="n">
+      <c r="H31" s="12" t="n">
         <f aca="false">B31*LN(G31)</f>
         <v>-13.6948547749176</v>
       </c>
@@ -8326,14 +8304,14 @@
         <f aca="false">(I31+'Model Parameters'!$D$11)/('Model Parameters'!$D$9+'Model Parameters'!$D$11*'Model Parameters'!$D$10)</f>
         <v>4.40862680092405E-006</v>
       </c>
-      <c r="K31" s="13" t="n">
+      <c r="K31" s="12" t="n">
         <f aca="false">B31*LN(J31)</f>
         <v>-12.3319473000057</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B32" s="6" t="n">
         <v>1</v>
@@ -8345,7 +8323,7 @@
         <f aca="false">(C32+'Model Parameters'!$B$11)/('Model Parameters'!$B$9+'Model Parameters'!$B$11*'Model Parameters'!$B$10)</f>
         <v>1.70139931586734E-005</v>
       </c>
-      <c r="E32" s="13" t="n">
+      <c r="E32" s="12" t="n">
         <f aca="false">B32*LN(D32)</f>
         <v>-10.9814744255105</v>
       </c>
@@ -8356,7 +8334,7 @@
         <f aca="false">(F32+'Model Parameters'!$C$11)/('Model Parameters'!$C$9+'Model Parameters'!$C$11*'Model Parameters'!$C$10)</f>
         <v>1.12823648739365E-006</v>
       </c>
-      <c r="H32" s="13" t="n">
+      <c r="H32" s="12" t="n">
         <f aca="false">B32*LN(G32)</f>
         <v>-13.6948547749176</v>
       </c>
@@ -8367,14 +8345,14 @@
         <f aca="false">(I32+'Model Parameters'!$D$11)/('Model Parameters'!$D$9+'Model Parameters'!$D$11*'Model Parameters'!$D$10)</f>
         <v>4.40862680092405E-006</v>
       </c>
-      <c r="K32" s="13" t="n">
+      <c r="K32" s="12" t="n">
         <f aca="false">B32*LN(J32)</f>
         <v>-12.3319473000057</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B33" s="6" t="n">
         <v>1</v>
@@ -8386,7 +8364,7 @@
         <f aca="false">(C33+'Model Parameters'!$B$11)/('Model Parameters'!$B$9+'Model Parameters'!$B$11*'Model Parameters'!$B$10)</f>
         <v>8.50699657933668E-007</v>
       </c>
-      <c r="E33" s="13" t="n">
+      <c r="E33" s="12" t="n">
         <f aca="false">B33*LN(D33)</f>
         <v>-13.9772066990645</v>
       </c>
@@ -8397,7 +8375,7 @@
         <f aca="false">(F33+'Model Parameters'!$C$11)/('Model Parameters'!$C$9+'Model Parameters'!$C$11*'Model Parameters'!$C$10)</f>
         <v>1.12823648739365E-006</v>
       </c>
-      <c r="H33" s="13" t="n">
+      <c r="H33" s="12" t="n">
         <f aca="false">B33*LN(G33)</f>
         <v>-13.6948547749176</v>
       </c>
@@ -8408,14 +8386,14 @@
         <f aca="false">(I33+'Model Parameters'!$D$11)/('Model Parameters'!$D$9+'Model Parameters'!$D$11*'Model Parameters'!$D$10)</f>
         <v>4.40862680092405E-006</v>
       </c>
-      <c r="K33" s="13" t="n">
+      <c r="K33" s="12" t="n">
         <f aca="false">B33*LN(J33)</f>
         <v>-12.3319473000057</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B34" s="6" t="n">
         <v>1</v>
@@ -8427,7 +8405,7 @@
         <f aca="false">(C34+'Model Parameters'!$B$11)/('Model Parameters'!$B$9+'Model Parameters'!$B$11*'Model Parameters'!$B$10)</f>
         <v>8.50699657933668E-007</v>
       </c>
-      <c r="E34" s="13" t="n">
+      <c r="E34" s="12" t="n">
         <f aca="false">B34*LN(D34)</f>
         <v>-13.9772066990645</v>
       </c>
@@ -8438,7 +8416,7 @@
         <f aca="false">(F34+'Model Parameters'!$C$11)/('Model Parameters'!$C$9+'Model Parameters'!$C$11*'Model Parameters'!$C$10)</f>
         <v>1.12823648739365E-006</v>
       </c>
-      <c r="H34" s="13" t="n">
+      <c r="H34" s="12" t="n">
         <f aca="false">B34*LN(G34)</f>
         <v>-13.6948547749176</v>
       </c>
@@ -8449,14 +8427,14 @@
         <f aca="false">(I34+'Model Parameters'!$D$11)/('Model Parameters'!$D$9+'Model Parameters'!$D$11*'Model Parameters'!$D$10)</f>
         <v>4.40862680092405E-006</v>
       </c>
-      <c r="K34" s="13" t="n">
+      <c r="K34" s="12" t="n">
         <f aca="false">B34*LN(J34)</f>
         <v>-12.3319473000057</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B35" s="6" t="n">
         <v>1</v>
@@ -8468,7 +8446,7 @@
         <f aca="false">(C35+'Model Parameters'!$B$11)/('Model Parameters'!$B$9+'Model Parameters'!$B$11*'Model Parameters'!$B$10)</f>
         <v>0.000265418293275304</v>
       </c>
-      <c r="E35" s="13" t="n">
+      <c r="E35" s="12" t="n">
         <f aca="false">B35*LN(D35)</f>
         <v>-8.23420351125501</v>
       </c>
@@ -8479,7 +8457,7 @@
         <f aca="false">(F35+'Model Parameters'!$C$11)/('Model Parameters'!$C$9+'Model Parameters'!$C$11*'Model Parameters'!$C$10)</f>
         <v>1.12823648739365E-006</v>
       </c>
-      <c r="H35" s="13" t="n">
+      <c r="H35" s="12" t="n">
         <f aca="false">B35*LN(G35)</f>
         <v>-13.6948547749176</v>
       </c>
@@ -8490,14 +8468,14 @@
         <f aca="false">(I35+'Model Parameters'!$D$11)/('Model Parameters'!$D$9+'Model Parameters'!$D$11*'Model Parameters'!$D$10)</f>
         <v>4.40862680092405E-006</v>
       </c>
-      <c r="K35" s="13" t="n">
+      <c r="K35" s="12" t="n">
         <f aca="false">B35*LN(J35)</f>
         <v>-12.3319473000057</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B36" s="6" t="n">
         <v>1</v>
@@ -8509,7 +8487,7 @@
         <f aca="false">(C36+'Model Parameters'!$B$11)/('Model Parameters'!$B$9+'Model Parameters'!$B$11*'Model Parameters'!$B$10)</f>
         <v>0.000230539607300024</v>
       </c>
-      <c r="E36" s="13" t="n">
+      <c r="E36" s="12" t="n">
         <f aca="false">B36*LN(D36)</f>
         <v>-8.37508787818479</v>
       </c>
@@ -8520,7 +8498,7 @@
         <f aca="false">(F36+'Model Parameters'!$C$11)/('Model Parameters'!$C$9+'Model Parameters'!$C$11*'Model Parameters'!$C$10)</f>
         <v>1.12823648739365E-006</v>
       </c>
-      <c r="H36" s="13" t="n">
+      <c r="H36" s="12" t="n">
         <f aca="false">B36*LN(G36)</f>
         <v>-13.6948547749176</v>
       </c>
@@ -8531,14 +8509,14 @@
         <f aca="false">(I36+'Model Parameters'!$D$11)/('Model Parameters'!$D$9+'Model Parameters'!$D$11*'Model Parameters'!$D$10)</f>
         <v>4.40862680092405E-006</v>
       </c>
-      <c r="K36" s="13" t="n">
+      <c r="K36" s="12" t="n">
         <f aca="false">B36*LN(J36)</f>
         <v>-12.3319473000057</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B37" s="6" t="n">
         <v>1</v>
@@ -8550,7 +8528,7 @@
         <f aca="false">(C37+'Model Parameters'!$B$11)/('Model Parameters'!$B$9+'Model Parameters'!$B$11*'Model Parameters'!$B$10)</f>
         <v>2.0416791790408E-005</v>
       </c>
-      <c r="E37" s="13" t="n">
+      <c r="E37" s="12" t="n">
         <f aca="false">B37*LN(D37)</f>
         <v>-10.7991528687165</v>
       </c>
@@ -8561,7 +8539,7 @@
         <f aca="false">(F37+'Model Parameters'!$C$11)/('Model Parameters'!$C$9+'Model Parameters'!$C$11*'Model Parameters'!$C$10)</f>
         <v>1.12823648739365E-006</v>
       </c>
-      <c r="H37" s="13" t="n">
+      <c r="H37" s="12" t="n">
         <f aca="false">B37*LN(G37)</f>
         <v>-13.6948547749176</v>
       </c>
@@ -8572,14 +8550,14 @@
         <f aca="false">(I37+'Model Parameters'!$D$11)/('Model Parameters'!$D$9+'Model Parameters'!$D$11*'Model Parameters'!$D$10)</f>
         <v>4.40862680092405E-006</v>
       </c>
-      <c r="K37" s="13" t="n">
+      <c r="K37" s="12" t="n">
         <f aca="false">B37*LN(J37)</f>
         <v>-12.3319473000057</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="6" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B38" s="6" t="n">
         <v>1</v>
@@ -8591,7 +8569,7 @@
         <f aca="false">(C38+'Model Parameters'!$B$11)/('Model Parameters'!$B$9+'Model Parameters'!$B$11*'Model Parameters'!$B$10)</f>
         <v>2.0416791790408E-005</v>
       </c>
-      <c r="E38" s="13" t="n">
+      <c r="E38" s="12" t="n">
         <f aca="false">B38*LN(D38)</f>
         <v>-10.7991528687165</v>
       </c>
@@ -8602,7 +8580,7 @@
         <f aca="false">(F38+'Model Parameters'!$C$11)/('Model Parameters'!$C$9+'Model Parameters'!$C$11*'Model Parameters'!$C$10)</f>
         <v>1.12823648739365E-006</v>
       </c>
-      <c r="H38" s="13" t="n">
+      <c r="H38" s="12" t="n">
         <f aca="false">B38*LN(G38)</f>
         <v>-13.6948547749176</v>
       </c>
@@ -8613,14 +8591,14 @@
         <f aca="false">(I38+'Model Parameters'!$D$11)/('Model Parameters'!$D$9+'Model Parameters'!$D$11*'Model Parameters'!$D$10)</f>
         <v>4.40862680092405E-006</v>
       </c>
-      <c r="K38" s="13" t="n">
+      <c r="K38" s="12" t="n">
         <f aca="false">B38*LN(J38)</f>
         <v>-12.3319473000057</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="6" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B39" s="6" t="n">
         <v>1</v>
@@ -8632,7 +8610,7 @@
         <f aca="false">(C39+'Model Parameters'!$B$11)/('Model Parameters'!$B$9+'Model Parameters'!$B$11*'Model Parameters'!$B$10)</f>
         <v>2.0416791790408E-005</v>
       </c>
-      <c r="E39" s="13" t="n">
+      <c r="E39" s="12" t="n">
         <f aca="false">B39*LN(D39)</f>
         <v>-10.7991528687165</v>
       </c>
@@ -8643,7 +8621,7 @@
         <f aca="false">(F39+'Model Parameters'!$C$11)/('Model Parameters'!$C$9+'Model Parameters'!$C$11*'Model Parameters'!$C$10)</f>
         <v>1.12823648739365E-006</v>
       </c>
-      <c r="H39" s="13" t="n">
+      <c r="H39" s="12" t="n">
         <f aca="false">B39*LN(G39)</f>
         <v>-13.6948547749176</v>
       </c>
@@ -8654,14 +8632,14 @@
         <f aca="false">(I39+'Model Parameters'!$D$11)/('Model Parameters'!$D$9+'Model Parameters'!$D$11*'Model Parameters'!$D$10)</f>
         <v>0.00277743488458215</v>
       </c>
-      <c r="K39" s="13" t="n">
+      <c r="K39" s="12" t="n">
         <f aca="false">B39*LN(J39)</f>
         <v>-5.88622748062012</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="6" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B40" s="6" t="n">
         <v>1</v>
@@ -8673,7 +8651,7 @@
         <f aca="false">(C40+'Model Parameters'!$B$11)/('Model Parameters'!$B$9+'Model Parameters'!$B$11*'Model Parameters'!$B$10)</f>
         <v>2.0416791790408E-005</v>
       </c>
-      <c r="E40" s="13" t="n">
+      <c r="E40" s="12" t="n">
         <f aca="false">B40*LN(D40)</f>
         <v>-10.7991528687165</v>
       </c>
@@ -8684,7 +8662,7 @@
         <f aca="false">(F40+'Model Parameters'!$C$11)/('Model Parameters'!$C$9+'Model Parameters'!$C$11*'Model Parameters'!$C$10)</f>
         <v>1.12823648739365E-006</v>
       </c>
-      <c r="H40" s="13" t="n">
+      <c r="H40" s="12" t="n">
         <f aca="false">B40*LN(G40)</f>
         <v>-13.6948547749176</v>
       </c>
@@ -8695,14 +8673,14 @@
         <f aca="false">(I40+'Model Parameters'!$D$11)/('Model Parameters'!$D$9+'Model Parameters'!$D$11*'Model Parameters'!$D$10)</f>
         <v>4.40862680092405E-006</v>
       </c>
-      <c r="K40" s="13" t="n">
+      <c r="K40" s="12" t="n">
         <f aca="false">B40*LN(J40)</f>
         <v>-12.3319473000057</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B41" s="6" t="n">
         <v>1</v>
@@ -8714,7 +8692,7 @@
         <f aca="false">(C41+'Model Parameters'!$B$11)/('Model Parameters'!$B$9+'Model Parameters'!$B$11*'Model Parameters'!$B$10)</f>
         <v>0.000740108702402291</v>
       </c>
-      <c r="E41" s="13" t="n">
+      <c r="E41" s="12" t="n">
         <f aca="false">B41*LN(D41)</f>
         <v>-7.20871348741586</v>
       </c>
@@ -8725,7 +8703,7 @@
         <f aca="false">(F41+'Model Parameters'!$C$11)/('Model Parameters'!$C$9+'Model Parameters'!$C$11*'Model Parameters'!$C$10)</f>
         <v>1.12823648739365E-006</v>
       </c>
-      <c r="H41" s="13" t="n">
+      <c r="H41" s="12" t="n">
         <f aca="false">B41*LN(G41)</f>
         <v>-13.6948547749176</v>
       </c>
@@ -8736,14 +8714,14 @@
         <f aca="false">(I41+'Model Parameters'!$D$11)/('Model Parameters'!$D$9+'Model Parameters'!$D$11*'Model Parameters'!$D$10)</f>
         <v>4.40862680092405E-006</v>
       </c>
-      <c r="K41" s="13" t="n">
+      <c r="K41" s="12" t="n">
         <f aca="false">B41*LN(J41)</f>
         <v>-12.3319473000057</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="6" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B42" s="6" t="n">
         <v>1</v>
@@ -8755,7 +8733,7 @@
         <f aca="false">(C42+'Model Parameters'!$B$11)/('Model Parameters'!$B$9+'Model Parameters'!$B$11*'Model Parameters'!$B$10)</f>
         <v>0.000265418293275304</v>
       </c>
-      <c r="E42" s="13" t="n">
+      <c r="E42" s="12" t="n">
         <f aca="false">B42*LN(D42)</f>
         <v>-8.23420351125501</v>
       </c>
@@ -8766,7 +8744,7 @@
         <f aca="false">(F42+'Model Parameters'!$C$11)/('Model Parameters'!$C$9+'Model Parameters'!$C$11*'Model Parameters'!$C$10)</f>
         <v>1.12823648739365E-006</v>
       </c>
-      <c r="H42" s="13" t="n">
+      <c r="H42" s="12" t="n">
         <f aca="false">B42*LN(G42)</f>
         <v>-13.6948547749176</v>
       </c>
@@ -8777,14 +8755,14 @@
         <f aca="false">(I42+'Model Parameters'!$D$11)/('Model Parameters'!$D$9+'Model Parameters'!$D$11*'Model Parameters'!$D$10)</f>
         <v>4.40862680092405E-006</v>
       </c>
-      <c r="K42" s="13" t="n">
+      <c r="K42" s="12" t="n">
         <f aca="false">B42*LN(J42)</f>
         <v>-12.3319473000057</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="6" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B43" s="6" t="n">
         <v>1</v>
@@ -8796,7 +8774,7 @@
         <f aca="false">(C43+'Model Parameters'!$B$11)/('Model Parameters'!$B$9+'Model Parameters'!$B$11*'Model Parameters'!$B$10)</f>
         <v>0.000265418293275304</v>
       </c>
-      <c r="E43" s="13" t="n">
+      <c r="E43" s="12" t="n">
         <f aca="false">B43*LN(D43)</f>
         <v>-8.23420351125501</v>
       </c>
@@ -8807,7 +8785,7 @@
         <f aca="false">(F43+'Model Parameters'!$C$11)/('Model Parameters'!$C$9+'Model Parameters'!$C$11*'Model Parameters'!$C$10)</f>
         <v>1.12823648739365E-006</v>
       </c>
-      <c r="H43" s="13" t="n">
+      <c r="H43" s="12" t="n">
         <f aca="false">B43*LN(G43)</f>
         <v>-13.6948547749176</v>
       </c>
@@ -8818,14 +8796,14 @@
         <f aca="false">(I43+'Model Parameters'!$D$11)/('Model Parameters'!$D$9+'Model Parameters'!$D$11*'Model Parameters'!$D$10)</f>
         <v>4.40862680092405E-006</v>
       </c>
-      <c r="K43" s="13" t="n">
+      <c r="K43" s="12" t="n">
         <f aca="false">B43*LN(J43)</f>
         <v>-12.3319473000057</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="6" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B44" s="6" t="n">
         <v>1</v>
@@ -8837,7 +8815,7 @@
         <f aca="false">(C44+'Model Parameters'!$B$11)/('Model Parameters'!$B$9+'Model Parameters'!$B$11*'Model Parameters'!$B$10)</f>
         <v>0.000826880067511525</v>
       </c>
-      <c r="E44" s="13" t="n">
+      <c r="E44" s="12" t="n">
         <f aca="false">B44*LN(D44)</f>
         <v>-7.09785089460405</v>
       </c>
@@ -8848,7 +8826,7 @@
         <f aca="false">(F44+'Model Parameters'!$C$11)/('Model Parameters'!$C$9+'Model Parameters'!$C$11*'Model Parameters'!$C$10)</f>
         <v>1.12823648739365E-006</v>
       </c>
-      <c r="H44" s="13" t="n">
+      <c r="H44" s="12" t="n">
         <f aca="false">B44*LN(G44)</f>
         <v>-13.6948547749176</v>
       </c>
@@ -8859,14 +8837,14 @@
         <f aca="false">(I44+'Model Parameters'!$D$11)/('Model Parameters'!$D$9+'Model Parameters'!$D$11*'Model Parameters'!$D$10)</f>
         <v>4.40862680092405E-006</v>
       </c>
-      <c r="K44" s="13" t="n">
+      <c r="K44" s="12" t="n">
         <f aca="false">B44*LN(J44)</f>
         <v>-12.3319473000057</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="6" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B45" s="6" t="n">
         <v>1</v>
@@ -8878,7 +8856,7 @@
         <f aca="false">(C45+'Model Parameters'!$B$11)/('Model Parameters'!$B$9+'Model Parameters'!$B$11*'Model Parameters'!$B$10)</f>
         <v>1.61632935007397E-005</v>
       </c>
-      <c r="E45" s="13" t="n">
+      <c r="E45" s="12" t="n">
         <f aca="false">B45*LN(D45)</f>
         <v>-11.0327677198981</v>
       </c>
@@ -8889,7 +8867,7 @@
         <f aca="false">(F45+'Model Parameters'!$C$11)/('Model Parameters'!$C$9+'Model Parameters'!$C$11*'Model Parameters'!$C$10)</f>
         <v>1.12823648739365E-006</v>
       </c>
-      <c r="H45" s="13" t="n">
+      <c r="H45" s="12" t="n">
         <f aca="false">B45*LN(G45)</f>
         <v>-13.6948547749176</v>
       </c>
@@ -8900,14 +8878,14 @@
         <f aca="false">(I45+'Model Parameters'!$D$11)/('Model Parameters'!$D$9+'Model Parameters'!$D$11*'Model Parameters'!$D$10)</f>
         <v>4.40862680092405E-006</v>
       </c>
-      <c r="K45" s="13" t="n">
+      <c r="K45" s="12" t="n">
         <f aca="false">B45*LN(J45)</f>
         <v>-12.3319473000057</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="6" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B46" s="6" t="n">
         <v>1</v>
@@ -8919,7 +8897,7 @@
         <f aca="false">(C46+'Model Parameters'!$B$11)/('Model Parameters'!$B$9+'Model Parameters'!$B$11*'Model Parameters'!$B$10)</f>
         <v>0.00132709146637652</v>
       </c>
-      <c r="E46" s="13" t="n">
+      <c r="E46" s="12" t="n">
         <f aca="false">B46*LN(D46)</f>
         <v>-6.62476559882091</v>
       </c>
@@ -8930,7 +8908,7 @@
         <f aca="false">(F46+'Model Parameters'!$C$11)/('Model Parameters'!$C$9+'Model Parameters'!$C$11*'Model Parameters'!$C$10)</f>
         <v>1.12823648739365E-006</v>
       </c>
-      <c r="H46" s="13" t="n">
+      <c r="H46" s="12" t="n">
         <f aca="false">B46*LN(G46)</f>
         <v>-13.6948547749176</v>
       </c>
@@ -8941,14 +8919,14 @@
         <f aca="false">(I46+'Model Parameters'!$D$11)/('Model Parameters'!$D$9+'Model Parameters'!$D$11*'Model Parameters'!$D$10)</f>
         <v>4.40862680092405E-006</v>
       </c>
-      <c r="K46" s="13" t="n">
+      <c r="K46" s="12" t="n">
         <f aca="false">B46*LN(J46)</f>
         <v>-12.3319473000057</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="6" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B47" s="6" t="n">
         <v>1</v>
@@ -8960,7 +8938,7 @@
         <f aca="false">(C47+'Model Parameters'!$B$11)/('Model Parameters'!$B$9+'Model Parameters'!$B$11*'Model Parameters'!$B$10)</f>
         <v>1.87153924745407E-005</v>
       </c>
-      <c r="E47" s="13" t="n">
+      <c r="E47" s="12" t="n">
         <f aca="false">B47*LN(D47)</f>
         <v>-10.8861642457062</v>
       </c>
@@ -8971,7 +8949,7 @@
         <f aca="false">(F47+'Model Parameters'!$C$11)/('Model Parameters'!$C$9+'Model Parameters'!$C$11*'Model Parameters'!$C$10)</f>
         <v>1.12823648739365E-006</v>
       </c>
-      <c r="H47" s="13" t="n">
+      <c r="H47" s="12" t="n">
         <f aca="false">B47*LN(G47)</f>
         <v>-13.6948547749176</v>
       </c>
@@ -8982,14 +8960,14 @@
         <f aca="false">(I47+'Model Parameters'!$D$11)/('Model Parameters'!$D$9+'Model Parameters'!$D$11*'Model Parameters'!$D$10)</f>
         <v>4.40862680092405E-006</v>
       </c>
-      <c r="K47" s="13" t="n">
+      <c r="K47" s="12" t="n">
         <f aca="false">B47*LN(J47)</f>
         <v>-12.3319473000057</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="6" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B48" s="6" t="n">
         <v>1</v>
@@ -9001,7 +8979,7 @@
         <f aca="false">(C48+'Model Parameters'!$B$11)/('Model Parameters'!$B$9+'Model Parameters'!$B$11*'Model Parameters'!$B$10)</f>
         <v>4.25349828966834E-006</v>
       </c>
-      <c r="E48" s="13" t="n">
+      <c r="E48" s="12" t="n">
         <f aca="false">B48*LN(D48)</f>
         <v>-12.3677687866304</v>
       </c>
@@ -9012,7 +8990,7 @@
         <f aca="false">(F48+'Model Parameters'!$C$11)/('Model Parameters'!$C$9+'Model Parameters'!$C$11*'Model Parameters'!$C$10)</f>
         <v>1.12823648739365E-006</v>
       </c>
-      <c r="H48" s="13" t="n">
+      <c r="H48" s="12" t="n">
         <f aca="false">B48*LN(G48)</f>
         <v>-13.6948547749176</v>
       </c>
@@ -9023,14 +9001,14 @@
         <f aca="false">(I48+'Model Parameters'!$D$11)/('Model Parameters'!$D$9+'Model Parameters'!$D$11*'Model Parameters'!$D$10)</f>
         <v>4.40862680092405E-006</v>
       </c>
-      <c r="K48" s="13" t="n">
+      <c r="K48" s="12" t="n">
         <f aca="false">B48*LN(J48)</f>
         <v>-12.3319473000057</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="6" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B49" s="6" t="n">
         <v>1</v>
@@ -9042,7 +9020,7 @@
         <f aca="false">(C49+'Model Parameters'!$B$11)/('Model Parameters'!$B$9+'Model Parameters'!$B$11*'Model Parameters'!$B$10)</f>
         <v>1.70139931586734E-006</v>
       </c>
-      <c r="E49" s="13" t="n">
+      <c r="E49" s="12" t="n">
         <f aca="false">B49*LN(D49)</f>
         <v>-13.2840595185045</v>
       </c>
@@ -9053,7 +9031,7 @@
         <f aca="false">(F49+'Model Parameters'!$C$11)/('Model Parameters'!$C$9+'Model Parameters'!$C$11*'Model Parameters'!$C$10)</f>
         <v>1.12823648739365E-006</v>
       </c>
-      <c r="H49" s="13" t="n">
+      <c r="H49" s="12" t="n">
         <f aca="false">B49*LN(G49)</f>
         <v>-13.6948547749176</v>
       </c>
@@ -9064,14 +9042,14 @@
         <f aca="false">(I49+'Model Parameters'!$D$11)/('Model Parameters'!$D$9+'Model Parameters'!$D$11*'Model Parameters'!$D$10)</f>
         <v>4.40862680092405E-006</v>
       </c>
-      <c r="K49" s="13" t="n">
+      <c r="K49" s="12" t="n">
         <f aca="false">B49*LN(J49)</f>
         <v>-12.3319473000057</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="6" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B50" s="6" t="n">
         <v>1</v>
@@ -9083,7 +9061,7 @@
         <f aca="false">(C50+'Model Parameters'!$B$11)/('Model Parameters'!$B$9+'Model Parameters'!$B$11*'Model Parameters'!$B$10)</f>
         <v>1.61632935007397E-005</v>
       </c>
-      <c r="E50" s="13" t="n">
+      <c r="E50" s="12" t="n">
         <f aca="false">B50*LN(D50)</f>
         <v>-11.0327677198981</v>
       </c>
@@ -9094,7 +9072,7 @@
         <f aca="false">(F50+'Model Parameters'!$C$11)/('Model Parameters'!$C$9+'Model Parameters'!$C$11*'Model Parameters'!$C$10)</f>
         <v>1.12823648739365E-006</v>
       </c>
-      <c r="H50" s="13" t="n">
+      <c r="H50" s="12" t="n">
         <f aca="false">B50*LN(G50)</f>
         <v>-13.6948547749176</v>
       </c>
@@ -9105,14 +9083,14 @@
         <f aca="false">(I50+'Model Parameters'!$D$11)/('Model Parameters'!$D$9+'Model Parameters'!$D$11*'Model Parameters'!$D$10)</f>
         <v>4.40862680092405E-006</v>
       </c>
-      <c r="K50" s="13" t="n">
+      <c r="K50" s="12" t="n">
         <f aca="false">B50*LN(J50)</f>
         <v>-12.3319473000057</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="6" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B51" s="6" t="n">
         <v>1</v>
@@ -9124,7 +9102,7 @@
         <f aca="false">(C51+'Model Parameters'!$B$11)/('Model Parameters'!$B$9+'Model Parameters'!$B$11*'Model Parameters'!$B$10)</f>
         <v>1.61632935007397E-005</v>
       </c>
-      <c r="E51" s="13" t="n">
+      <c r="E51" s="12" t="n">
         <f aca="false">B51*LN(D51)</f>
         <v>-11.0327677198981</v>
       </c>
@@ -9135,7 +9113,7 @@
         <f aca="false">(F51+'Model Parameters'!$C$11)/('Model Parameters'!$C$9+'Model Parameters'!$C$11*'Model Parameters'!$C$10)</f>
         <v>1.12823648739365E-006</v>
       </c>
-      <c r="H51" s="13" t="n">
+      <c r="H51" s="12" t="n">
         <f aca="false">B51*LN(G51)</f>
         <v>-13.6948547749176</v>
       </c>
@@ -9146,14 +9124,14 @@
         <f aca="false">(I51+'Model Parameters'!$D$11)/('Model Parameters'!$D$9+'Model Parameters'!$D$11*'Model Parameters'!$D$10)</f>
         <v>4.40862680092405E-006</v>
       </c>
-      <c r="K51" s="13" t="n">
+      <c r="K51" s="12" t="n">
         <f aca="false">B51*LN(J51)</f>
         <v>-12.3319473000057</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="6" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B52" s="6" t="n">
         <v>1</v>
@@ -9165,7 +9143,7 @@
         <f aca="false">(C52+'Model Parameters'!$B$11)/('Model Parameters'!$B$9+'Model Parameters'!$B$11*'Model Parameters'!$B$10)</f>
         <v>0.000715438412322214</v>
       </c>
-      <c r="E52" s="13" t="n">
+      <c r="E52" s="12" t="n">
         <f aca="false">B52*LN(D52)</f>
         <v>-7.24261503909154</v>
       </c>
@@ -9176,7 +9154,7 @@
         <f aca="false">(F52+'Model Parameters'!$C$11)/('Model Parameters'!$C$9+'Model Parameters'!$C$11*'Model Parameters'!$C$10)</f>
         <v>1.12823648739365E-006</v>
       </c>
-      <c r="H52" s="13" t="n">
+      <c r="H52" s="12" t="n">
         <f aca="false">B52*LN(G52)</f>
         <v>-13.6948547749176</v>
       </c>
@@ -9187,14 +9165,14 @@
         <f aca="false">(I52+'Model Parameters'!$D$11)/('Model Parameters'!$D$9+'Model Parameters'!$D$11*'Model Parameters'!$D$10)</f>
         <v>4.40862680092405E-006</v>
       </c>
-      <c r="K52" s="13" t="n">
+      <c r="K52" s="12" t="n">
         <f aca="false">B52*LN(J52)</f>
         <v>-12.3319473000057</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="6" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B53" s="6" t="n">
         <v>1</v>
@@ -9206,7 +9184,7 @@
         <f aca="false">(C53+'Model Parameters'!$B$11)/('Model Parameters'!$B$9+'Model Parameters'!$B$11*'Model Parameters'!$B$10)</f>
         <v>8.50699657933668E-007</v>
       </c>
-      <c r="E53" s="13" t="n">
+      <c r="E53" s="12" t="n">
         <f aca="false">B53*LN(D53)</f>
         <v>-13.9772066990645</v>
       </c>
@@ -9217,7 +9195,7 @@
         <f aca="false">(F53+'Model Parameters'!$C$11)/('Model Parameters'!$C$9+'Model Parameters'!$C$11*'Model Parameters'!$C$10)</f>
         <v>1.12823648739365E-006</v>
       </c>
-      <c r="H53" s="13" t="n">
+      <c r="H53" s="12" t="n">
         <f aca="false">B53*LN(G53)</f>
         <v>-13.6948547749176</v>
       </c>
@@ -9228,14 +9206,14 @@
         <f aca="false">(I53+'Model Parameters'!$D$11)/('Model Parameters'!$D$9+'Model Parameters'!$D$11*'Model Parameters'!$D$10)</f>
         <v>4.40862680092405E-006</v>
       </c>
-      <c r="K53" s="13" t="n">
+      <c r="K53" s="12" t="n">
         <f aca="false">B53*LN(J53)</f>
         <v>-12.3319473000057</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B54" s="6" t="n">
         <v>1</v>
@@ -9247,7 +9225,7 @@
         <f aca="false">(C54+'Model Parameters'!$B$11)/('Model Parameters'!$B$9+'Model Parameters'!$B$11*'Model Parameters'!$B$10)</f>
         <v>0.000831984265459127</v>
       </c>
-      <c r="E54" s="13" t="n">
+      <c r="E54" s="12" t="n">
         <f aca="false">B54*LN(D54)</f>
         <v>-7.09169702902968</v>
       </c>
@@ -9258,7 +9236,7 @@
         <f aca="false">(F54+'Model Parameters'!$C$11)/('Model Parameters'!$C$9+'Model Parameters'!$C$11*'Model Parameters'!$C$10)</f>
         <v>1.12823648739365E-006</v>
       </c>
-      <c r="H54" s="13" t="n">
+      <c r="H54" s="12" t="n">
         <f aca="false">B54*LN(G54)</f>
         <v>-13.6948547749176</v>
       </c>
@@ -9269,14 +9247,14 @@
         <f aca="false">(I54+'Model Parameters'!$D$11)/('Model Parameters'!$D$9+'Model Parameters'!$D$11*'Model Parameters'!$D$10)</f>
         <v>4.40862680092405E-006</v>
       </c>
-      <c r="K54" s="13" t="n">
+      <c r="K54" s="12" t="n">
         <f aca="false">B54*LN(J54)</f>
         <v>-12.3319473000057</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="6" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B55" s="6" t="n">
         <v>1</v>
@@ -9288,7 +9266,7 @@
         <f aca="false">(C55+'Model Parameters'!$B$11)/('Model Parameters'!$B$9+'Model Parameters'!$B$11*'Model Parameters'!$B$10)</f>
         <v>1.61632935007397E-005</v>
       </c>
-      <c r="E55" s="13" t="n">
+      <c r="E55" s="12" t="n">
         <f aca="false">B55*LN(D55)</f>
         <v>-11.0327677198981</v>
       </c>
@@ -9299,7 +9277,7 @@
         <f aca="false">(F55+'Model Parameters'!$C$11)/('Model Parameters'!$C$9+'Model Parameters'!$C$11*'Model Parameters'!$C$10)</f>
         <v>1.12823648739365E-006</v>
       </c>
-      <c r="H55" s="13" t="n">
+      <c r="H55" s="12" t="n">
         <f aca="false">B55*LN(G55)</f>
         <v>-13.6948547749176</v>
       </c>
@@ -9310,14 +9288,14 @@
         <f aca="false">(I55+'Model Parameters'!$D$11)/('Model Parameters'!$D$9+'Model Parameters'!$D$11*'Model Parameters'!$D$10)</f>
         <v>4.40862680092405E-006</v>
       </c>
-      <c r="K55" s="13" t="n">
+      <c r="K55" s="12" t="n">
         <f aca="false">B55*LN(J55)</f>
         <v>-12.3319473000057</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="6" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B56" s="6" t="n">
         <v>1</v>
@@ -9329,7 +9307,7 @@
         <f aca="false">(C56+'Model Parameters'!$B$11)/('Model Parameters'!$B$9+'Model Parameters'!$B$11*'Model Parameters'!$B$10)</f>
         <v>1.61632935007397E-005</v>
       </c>
-      <c r="E56" s="13" t="n">
+      <c r="E56" s="12" t="n">
         <f aca="false">B56*LN(D56)</f>
         <v>-11.0327677198981</v>
       </c>
@@ -9340,7 +9318,7 @@
         <f aca="false">(F56+'Model Parameters'!$C$11)/('Model Parameters'!$C$9+'Model Parameters'!$C$11*'Model Parameters'!$C$10)</f>
         <v>1.12823648739365E-006</v>
       </c>
-      <c r="H56" s="13" t="n">
+      <c r="H56" s="12" t="n">
         <f aca="false">B56*LN(G56)</f>
         <v>-13.6948547749176</v>
       </c>
@@ -9351,14 +9329,14 @@
         <f aca="false">(I56+'Model Parameters'!$D$11)/('Model Parameters'!$D$9+'Model Parameters'!$D$11*'Model Parameters'!$D$10)</f>
         <v>4.40862680092405E-006</v>
       </c>
-      <c r="K56" s="13" t="n">
+      <c r="K56" s="12" t="n">
         <f aca="false">B56*LN(J56)</f>
         <v>-12.3319473000057</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="6" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B57" s="6" t="n">
         <v>1</v>
@@ -9370,7 +9348,7 @@
         <f aca="false">(C57+'Model Parameters'!$B$11)/('Model Parameters'!$B$9+'Model Parameters'!$B$11*'Model Parameters'!$B$10)</f>
         <v>0.000230539607300024</v>
       </c>
-      <c r="E57" s="13" t="n">
+      <c r="E57" s="12" t="n">
         <f aca="false">B57*LN(D57)</f>
         <v>-8.37508787818479</v>
       </c>
@@ -9381,7 +9359,7 @@
         <f aca="false">(F57+'Model Parameters'!$C$11)/('Model Parameters'!$C$9+'Model Parameters'!$C$11*'Model Parameters'!$C$10)</f>
         <v>1.12823648739365E-006</v>
       </c>
-      <c r="H57" s="13" t="n">
+      <c r="H57" s="12" t="n">
         <f aca="false">B57*LN(G57)</f>
         <v>-13.6948547749176</v>
       </c>
@@ -9392,14 +9370,14 @@
         <f aca="false">(I57+'Model Parameters'!$D$11)/('Model Parameters'!$D$9+'Model Parameters'!$D$11*'Model Parameters'!$D$10)</f>
         <v>4.40862680092405E-006</v>
       </c>
-      <c r="K57" s="13" t="n">
+      <c r="K57" s="12" t="n">
         <f aca="false">B57*LN(J57)</f>
         <v>-12.3319473000057</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="6" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B58" s="6" t="n">
         <v>1</v>
@@ -9411,7 +9389,7 @@
         <f aca="false">(C58+'Model Parameters'!$B$11)/('Model Parameters'!$B$9+'Model Parameters'!$B$11*'Model Parameters'!$B$10)</f>
         <v>0.000230539607300024</v>
       </c>
-      <c r="E58" s="13" t="n">
+      <c r="E58" s="12" t="n">
         <f aca="false">B58*LN(D58)</f>
         <v>-8.37508787818479</v>
       </c>
@@ -9422,7 +9400,7 @@
         <f aca="false">(F58+'Model Parameters'!$C$11)/('Model Parameters'!$C$9+'Model Parameters'!$C$11*'Model Parameters'!$C$10)</f>
         <v>1.12823648739365E-006</v>
       </c>
-      <c r="H58" s="13" t="n">
+      <c r="H58" s="12" t="n">
         <f aca="false">B58*LN(G58)</f>
         <v>-13.6948547749176</v>
       </c>
@@ -9433,14 +9411,14 @@
         <f aca="false">(I58+'Model Parameters'!$D$11)/('Model Parameters'!$D$9+'Model Parameters'!$D$11*'Model Parameters'!$D$10)</f>
         <v>4.40862680092405E-006</v>
       </c>
-      <c r="K58" s="13" t="n">
+      <c r="K58" s="12" t="n">
         <f aca="false">B58*LN(J58)</f>
         <v>-12.3319473000057</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="6" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B59" s="6" t="n">
         <v>1</v>
@@ -9452,7 +9430,7 @@
         <f aca="false">(C59+'Model Parameters'!$B$11)/('Model Parameters'!$B$9+'Model Parameters'!$B$11*'Model Parameters'!$B$10)</f>
         <v>0.00160782235349463</v>
       </c>
-      <c r="E59" s="13" t="n">
+      <c r="E59" s="12" t="n">
         <f aca="false">B59*LN(D59)</f>
         <v>-6.4328745910108</v>
       </c>
@@ -9463,7 +9441,7 @@
         <f aca="false">(F59+'Model Parameters'!$C$11)/('Model Parameters'!$C$9+'Model Parameters'!$C$11*'Model Parameters'!$C$10)</f>
         <v>0.00167881589324175</v>
       </c>
-      <c r="H59" s="13" t="n">
+      <c r="H59" s="12" t="n">
         <f aca="false">B59*LN(G59)</f>
         <v>-6.38966655952454</v>
       </c>
@@ -9474,14 +9452,14 @@
         <f aca="false">(I59+'Model Parameters'!$D$11)/('Model Parameters'!$D$9+'Model Parameters'!$D$11*'Model Parameters'!$D$10)</f>
         <v>0.0141957782989754</v>
       </c>
-      <c r="K59" s="13" t="n">
+      <c r="K59" s="12" t="n">
         <f aca="false">B59*LN(J59)</f>
         <v>-4.25481066146724</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B60" s="6" t="n">
         <v>1</v>
@@ -9493,7 +9471,7 @@
         <f aca="false">(C60+'Model Parameters'!$B$11)/('Model Parameters'!$B$9+'Model Parameters'!$B$11*'Model Parameters'!$B$10)</f>
         <v>1.61632935007397E-005</v>
       </c>
-      <c r="E60" s="13" t="n">
+      <c r="E60" s="12" t="n">
         <f aca="false">B60*LN(D60)</f>
         <v>-11.0327677198981</v>
       </c>
@@ -9504,7 +9482,7 @@
         <f aca="false">(F60+'Model Parameters'!$C$11)/('Model Parameters'!$C$9+'Model Parameters'!$C$11*'Model Parameters'!$C$10)</f>
         <v>1.12823648739365E-006</v>
       </c>
-      <c r="H60" s="13" t="n">
+      <c r="H60" s="12" t="n">
         <f aca="false">B60*LN(G60)</f>
         <v>-13.6948547749176</v>
       </c>
@@ -9515,14 +9493,14 @@
         <f aca="false">(I60+'Model Parameters'!$D$11)/('Model Parameters'!$D$9+'Model Parameters'!$D$11*'Model Parameters'!$D$10)</f>
         <v>4.40862680092405E-006</v>
       </c>
-      <c r="K60" s="13" t="n">
+      <c r="K60" s="12" t="n">
         <f aca="false">B60*LN(J60)</f>
         <v>-12.3319473000057</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="6" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B61" s="6" t="n">
         <v>1</v>
@@ -9534,7 +9512,7 @@
         <f aca="false">(C61+'Model Parameters'!$B$11)/('Model Parameters'!$B$9+'Model Parameters'!$B$11*'Model Parameters'!$B$10)</f>
         <v>0.000230539607300024</v>
       </c>
-      <c r="E61" s="13" t="n">
+      <c r="E61" s="12" t="n">
         <f aca="false">B61*LN(D61)</f>
         <v>-8.37508787818479</v>
       </c>
@@ -9545,7 +9523,7 @@
         <f aca="false">(F61+'Model Parameters'!$C$11)/('Model Parameters'!$C$9+'Model Parameters'!$C$11*'Model Parameters'!$C$10)</f>
         <v>1.12823648739365E-006</v>
       </c>
-      <c r="H61" s="13" t="n">
+      <c r="H61" s="12" t="n">
         <f aca="false">B61*LN(G61)</f>
         <v>-13.6948547749176</v>
       </c>
@@ -9556,14 +9534,14 @@
         <f aca="false">(I61+'Model Parameters'!$D$11)/('Model Parameters'!$D$9+'Model Parameters'!$D$11*'Model Parameters'!$D$10)</f>
         <v>4.40862680092405E-006</v>
       </c>
-      <c r="K61" s="13" t="n">
+      <c r="K61" s="12" t="n">
         <f aca="false">B61*LN(J61)</f>
         <v>-12.3319473000057</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="6" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B62" s="6" t="n">
         <v>1</v>
@@ -9575,7 +9553,7 @@
         <f aca="false">(C62+'Model Parameters'!$B$11)/('Model Parameters'!$B$9+'Model Parameters'!$B$11*'Model Parameters'!$B$10)</f>
         <v>0.000230539607300024</v>
       </c>
-      <c r="E62" s="13" t="n">
+      <c r="E62" s="12" t="n">
         <f aca="false">B62*LN(D62)</f>
         <v>-8.37508787818479</v>
       </c>
@@ -9586,7 +9564,7 @@
         <f aca="false">(F62+'Model Parameters'!$C$11)/('Model Parameters'!$C$9+'Model Parameters'!$C$11*'Model Parameters'!$C$10)</f>
         <v>1.12823648739365E-006</v>
       </c>
-      <c r="H62" s="13" t="n">
+      <c r="H62" s="12" t="n">
         <f aca="false">B62*LN(G62)</f>
         <v>-13.6948547749176</v>
       </c>
@@ -9597,14 +9575,14 @@
         <f aca="false">(I62+'Model Parameters'!$D$11)/('Model Parameters'!$D$9+'Model Parameters'!$D$11*'Model Parameters'!$D$10)</f>
         <v>4.40862680092405E-006</v>
       </c>
-      <c r="K62" s="13" t="n">
+      <c r="K62" s="12" t="n">
         <f aca="false">B62*LN(J62)</f>
         <v>-12.3319473000057</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="6" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B63" s="6" t="n">
         <v>1</v>
@@ -9616,7 +9594,7 @@
         <f aca="false">(C63+'Model Parameters'!$B$11)/('Model Parameters'!$B$9+'Model Parameters'!$B$11*'Model Parameters'!$B$10)</f>
         <v>0.00114759383855252</v>
       </c>
-      <c r="E63" s="13" t="n">
+      <c r="E63" s="12" t="n">
         <f aca="false">B63*LN(D63)</f>
         <v>-6.77008784285674</v>
       </c>
@@ -9627,7 +9605,7 @@
         <f aca="false">(F63+'Model Parameters'!$C$11)/('Model Parameters'!$C$9+'Model Parameters'!$C$11*'Model Parameters'!$C$10)</f>
         <v>1.12823648739365E-006</v>
       </c>
-      <c r="H63" s="13" t="n">
+      <c r="H63" s="12" t="n">
         <f aca="false">B63*LN(G63)</f>
         <v>-13.6948547749176</v>
       </c>
@@ -9638,14 +9616,14 @@
         <f aca="false">(I63+'Model Parameters'!$D$11)/('Model Parameters'!$D$9+'Model Parameters'!$D$11*'Model Parameters'!$D$10)</f>
         <v>4.40862680092405E-006</v>
       </c>
-      <c r="K63" s="13" t="n">
+      <c r="K63" s="12" t="n">
         <f aca="false">B63*LN(J63)</f>
         <v>-12.3319473000057</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="6" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B64" s="6" t="n">
         <v>1</v>
@@ -9657,7 +9635,7 @@
         <f aca="false">(C64+'Model Parameters'!$B$11)/('Model Parameters'!$B$9+'Model Parameters'!$B$11*'Model Parameters'!$B$10)</f>
         <v>0.00113993754163111</v>
       </c>
-      <c r="E64" s="13" t="n">
+      <c r="E64" s="12" t="n">
         <f aca="false">B64*LN(D64)</f>
         <v>-6.77678180611953</v>
       </c>
@@ -9668,7 +9646,7 @@
         <f aca="false">(F64+'Model Parameters'!$C$11)/('Model Parameters'!$C$9+'Model Parameters'!$C$11*'Model Parameters'!$C$10)</f>
         <v>1.12823648739365E-006</v>
       </c>
-      <c r="H64" s="13" t="n">
+      <c r="H64" s="12" t="n">
         <f aca="false">B64*LN(G64)</f>
         <v>-13.6948547749176</v>
       </c>
@@ -9679,14 +9657,14 @@
         <f aca="false">(I64+'Model Parameters'!$D$11)/('Model Parameters'!$D$9+'Model Parameters'!$D$11*'Model Parameters'!$D$10)</f>
         <v>4.40862680092405E-006</v>
       </c>
-      <c r="K64" s="13" t="n">
+      <c r="K64" s="12" t="n">
         <f aca="false">B64*LN(J64)</f>
         <v>-12.3319473000057</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="6" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B65" s="6" t="n">
         <v>1</v>
@@ -9698,7 +9676,7 @@
         <f aca="false">(C65+'Model Parameters'!$B$11)/('Model Parameters'!$B$9+'Model Parameters'!$B$11*'Model Parameters'!$B$10)</f>
         <v>0.000336026364883799</v>
       </c>
-      <c r="E65" s="13" t="n">
+      <c r="E65" s="12" t="n">
         <f aca="false">B65*LN(D65)</f>
         <v>-7.99832093416337</v>
       </c>
@@ -9709,7 +9687,7 @@
         <f aca="false">(F65+'Model Parameters'!$C$11)/('Model Parameters'!$C$9+'Model Parameters'!$C$11*'Model Parameters'!$C$10)</f>
         <v>1.12823648739365E-006</v>
       </c>
-      <c r="H65" s="13" t="n">
+      <c r="H65" s="12" t="n">
         <f aca="false">B65*LN(G65)</f>
         <v>-13.6948547749176</v>
       </c>
@@ -9720,14 +9698,14 @@
         <f aca="false">(I65+'Model Parameters'!$D$11)/('Model Parameters'!$D$9+'Model Parameters'!$D$11*'Model Parameters'!$D$10)</f>
         <v>4.40862680092405E-006</v>
       </c>
-      <c r="K65" s="13" t="n">
+      <c r="K65" s="12" t="n">
         <f aca="false">B65*LN(J65)</f>
         <v>-12.3319473000057</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="6" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B66" s="6" t="n">
         <v>1</v>
@@ -9739,7 +9717,7 @@
         <f aca="false">(C66+'Model Parameters'!$B$11)/('Model Parameters'!$B$9+'Model Parameters'!$B$11*'Model Parameters'!$B$10)</f>
         <v>1.61632935007397E-005</v>
       </c>
-      <c r="E66" s="13" t="n">
+      <c r="E66" s="12" t="n">
         <f aca="false">B66*LN(D66)</f>
         <v>-11.0327677198981</v>
       </c>
@@ -9750,7 +9728,7 @@
         <f aca="false">(F66+'Model Parameters'!$C$11)/('Model Parameters'!$C$9+'Model Parameters'!$C$11*'Model Parameters'!$C$10)</f>
         <v>1.12823648739365E-006</v>
       </c>
-      <c r="H66" s="13" t="n">
+      <c r="H66" s="12" t="n">
         <f aca="false">B66*LN(G66)</f>
         <v>-13.6948547749176</v>
       </c>
@@ -9761,14 +9739,14 @@
         <f aca="false">(I66+'Model Parameters'!$D$11)/('Model Parameters'!$D$9+'Model Parameters'!$D$11*'Model Parameters'!$D$10)</f>
         <v>4.40862680092405E-006</v>
       </c>
-      <c r="K66" s="13" t="n">
+      <c r="K66" s="12" t="n">
         <f aca="false">B66*LN(J66)</f>
         <v>-12.3319473000057</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="6" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B67" s="6" t="n">
         <v>1</v>
@@ -9780,7 +9758,7 @@
         <f aca="false">(C67+'Model Parameters'!$B$11)/('Model Parameters'!$B$9+'Model Parameters'!$B$11*'Model Parameters'!$B$10)</f>
         <v>1.61632935007397E-005</v>
       </c>
-      <c r="E67" s="13" t="n">
+      <c r="E67" s="12" t="n">
         <f aca="false">B67*LN(D67)</f>
         <v>-11.0327677198981</v>
       </c>
@@ -9791,7 +9769,7 @@
         <f aca="false">(F67+'Model Parameters'!$C$11)/('Model Parameters'!$C$9+'Model Parameters'!$C$11*'Model Parameters'!$C$10)</f>
         <v>1.12823648739365E-006</v>
       </c>
-      <c r="H67" s="13" t="n">
+      <c r="H67" s="12" t="n">
         <f aca="false">B67*LN(G67)</f>
         <v>-13.6948547749176</v>
       </c>
@@ -9802,14 +9780,14 @@
         <f aca="false">(I67+'Model Parameters'!$D$11)/('Model Parameters'!$D$9+'Model Parameters'!$D$11*'Model Parameters'!$D$10)</f>
         <v>4.40862680092405E-006</v>
       </c>
-      <c r="K67" s="13" t="n">
+      <c r="K67" s="12" t="n">
         <f aca="false">B67*LN(J67)</f>
         <v>-12.3319473000057</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="6" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B68" s="6" t="n">
         <v>1</v>
@@ -9821,7 +9799,7 @@
         <f aca="false">(C68+'Model Parameters'!$B$11)/('Model Parameters'!$B$9+'Model Parameters'!$B$11*'Model Parameters'!$B$10)</f>
         <v>1.61632935007397E-005</v>
       </c>
-      <c r="E68" s="13" t="n">
+      <c r="E68" s="12" t="n">
         <f aca="false">B68*LN(D68)</f>
         <v>-11.0327677198981</v>
       </c>
@@ -9832,7 +9810,7 @@
         <f aca="false">(F68+'Model Parameters'!$C$11)/('Model Parameters'!$C$9+'Model Parameters'!$C$11*'Model Parameters'!$C$10)</f>
         <v>1.12823648739365E-006</v>
       </c>
-      <c r="H68" s="13" t="n">
+      <c r="H68" s="12" t="n">
         <f aca="false">B68*LN(G68)</f>
         <v>-13.6948547749176</v>
       </c>
@@ -9843,14 +9821,14 @@
         <f aca="false">(I68+'Model Parameters'!$D$11)/('Model Parameters'!$D$9+'Model Parameters'!$D$11*'Model Parameters'!$D$10)</f>
         <v>4.40862680092405E-006</v>
       </c>
-      <c r="K68" s="13" t="n">
+      <c r="K68" s="12" t="n">
         <f aca="false">B68*LN(J68)</f>
         <v>-12.3319473000057</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="6" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B69" s="6" t="n">
         <v>1</v>
@@ -9862,7 +9840,7 @@
         <f aca="false">(C69+'Model Parameters'!$B$11)/('Model Parameters'!$B$9+'Model Parameters'!$B$11*'Model Parameters'!$B$10)</f>
         <v>0.000731601705822954</v>
       </c>
-      <c r="E69" s="13" t="n">
+      <c r="E69" s="12" t="n">
         <f aca="false">B69*LN(D69)</f>
         <v>-7.22027430981694</v>
       </c>
@@ -9873,7 +9851,7 @@
         <f aca="false">(F69+'Model Parameters'!$C$11)/('Model Parameters'!$C$9+'Model Parameters'!$C$11*'Model Parameters'!$C$10)</f>
         <v>1.12823648739365E-006</v>
       </c>
-      <c r="H69" s="13" t="n">
+      <c r="H69" s="12" t="n">
         <f aca="false">B69*LN(G69)</f>
         <v>-13.6948547749176</v>
       </c>
@@ -9884,14 +9862,14 @@
         <f aca="false">(I69+'Model Parameters'!$D$11)/('Model Parameters'!$D$9+'Model Parameters'!$D$11*'Model Parameters'!$D$10)</f>
         <v>4.40862680092405E-006</v>
       </c>
-      <c r="K69" s="13" t="n">
+      <c r="K69" s="12" t="n">
         <f aca="false">B69*LN(J69)</f>
         <v>-12.3319473000057</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="6" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B70" s="6" t="n">
         <v>1</v>
@@ -9903,7 +9881,7 @@
         <f aca="false">(C70+'Model Parameters'!$B$11)/('Model Parameters'!$B$9+'Model Parameters'!$B$11*'Model Parameters'!$B$10)</f>
         <v>0.000731601705822954</v>
       </c>
-      <c r="E70" s="13" t="n">
+      <c r="E70" s="12" t="n">
         <f aca="false">B70*LN(D70)</f>
         <v>-7.22027430981694</v>
       </c>
@@ -9914,7 +9892,7 @@
         <f aca="false">(F70+'Model Parameters'!$C$11)/('Model Parameters'!$C$9+'Model Parameters'!$C$11*'Model Parameters'!$C$10)</f>
         <v>1.12823648739365E-006</v>
       </c>
-      <c r="H70" s="13" t="n">
+      <c r="H70" s="12" t="n">
         <f aca="false">B70*LN(G70)</f>
         <v>-13.6948547749176</v>
       </c>
@@ -9925,14 +9903,14 @@
         <f aca="false">(I70+'Model Parameters'!$D$11)/('Model Parameters'!$D$9+'Model Parameters'!$D$11*'Model Parameters'!$D$10)</f>
         <v>4.40862680092405E-006</v>
       </c>
-      <c r="K70" s="13" t="n">
+      <c r="K70" s="12" t="n">
         <f aca="false">B70*LN(J70)</f>
         <v>-12.3319473000057</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="6" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B71" s="6" t="n">
         <v>1</v>
@@ -9944,7 +9922,7 @@
         <f aca="false">(C71+'Model Parameters'!$B$11)/('Model Parameters'!$B$9+'Model Parameters'!$B$11*'Model Parameters'!$B$10)</f>
         <v>0.00118077112521193</v>
       </c>
-      <c r="E71" s="13" t="n">
+      <c r="E71" s="12" t="n">
         <f aca="false">B71*LN(D71)</f>
         <v>-6.74158755799774</v>
       </c>
@@ -9955,7 +9933,7 @@
         <f aca="false">(F71+'Model Parameters'!$C$11)/('Model Parameters'!$C$9+'Model Parameters'!$C$11*'Model Parameters'!$C$10)</f>
         <v>1.12823648739365E-006</v>
       </c>
-      <c r="H71" s="13" t="n">
+      <c r="H71" s="12" t="n">
         <f aca="false">B71*LN(G71)</f>
         <v>-13.6948547749176</v>
       </c>
@@ -9966,14 +9944,14 @@
         <f aca="false">(I71+'Model Parameters'!$D$11)/('Model Parameters'!$D$9+'Model Parameters'!$D$11*'Model Parameters'!$D$10)</f>
         <v>4.40862680092405E-006</v>
       </c>
-      <c r="K71" s="13" t="n">
+      <c r="K71" s="12" t="n">
         <f aca="false">B71*LN(J71)</f>
         <v>-12.3319473000057</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="6" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B72" s="6" t="n">
         <v>1</v>
@@ -9985,7 +9963,7 @@
         <f aca="false">(C72+'Model Parameters'!$B$11)/('Model Parameters'!$B$9+'Model Parameters'!$B$11*'Model Parameters'!$B$10)</f>
         <v>1.61632935007397E-005</v>
       </c>
-      <c r="E72" s="13" t="n">
+      <c r="E72" s="12" t="n">
         <f aca="false">B72*LN(D72)</f>
         <v>-11.0327677198981</v>
       </c>
@@ -9996,7 +9974,7 @@
         <f aca="false">(F72+'Model Parameters'!$C$11)/('Model Parameters'!$C$9+'Model Parameters'!$C$11*'Model Parameters'!$C$10)</f>
         <v>1.12823648739365E-006</v>
       </c>
-      <c r="H72" s="13" t="n">
+      <c r="H72" s="12" t="n">
         <f aca="false">B72*LN(G72)</f>
         <v>-13.6948547749176</v>
       </c>
@@ -10007,14 +9985,14 @@
         <f aca="false">(I72+'Model Parameters'!$D$11)/('Model Parameters'!$D$9+'Model Parameters'!$D$11*'Model Parameters'!$D$10)</f>
         <v>4.40862680092405E-006</v>
       </c>
-      <c r="K72" s="13" t="n">
+      <c r="K72" s="12" t="n">
         <f aca="false">B72*LN(J72)</f>
         <v>-12.3319473000057</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="6" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B73" s="6" t="n">
         <v>1</v>
@@ -10026,7 +10004,7 @@
         <f aca="false">(C73+'Model Parameters'!$B$11)/('Model Parameters'!$B$9+'Model Parameters'!$B$11*'Model Parameters'!$B$10)</f>
         <v>0.00132709146637652</v>
       </c>
-      <c r="E73" s="13" t="n">
+      <c r="E73" s="12" t="n">
         <f aca="false">B73*LN(D73)</f>
         <v>-6.62476559882091</v>
       </c>
@@ -10037,7 +10015,7 @@
         <f aca="false">(F73+'Model Parameters'!$C$11)/('Model Parameters'!$C$9+'Model Parameters'!$C$11*'Model Parameters'!$C$10)</f>
         <v>1.12823648739365E-006</v>
       </c>
-      <c r="H73" s="13" t="n">
+      <c r="H73" s="12" t="n">
         <f aca="false">B73*LN(G73)</f>
         <v>-13.6948547749176</v>
       </c>
@@ -10048,14 +10026,14 @@
         <f aca="false">(I73+'Model Parameters'!$D$11)/('Model Parameters'!$D$9+'Model Parameters'!$D$11*'Model Parameters'!$D$10)</f>
         <v>4.40862680092405E-006</v>
       </c>
-      <c r="K73" s="13" t="n">
+      <c r="K73" s="12" t="n">
         <f aca="false">B73*LN(J73)</f>
         <v>-12.3319473000057</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="6" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B74" s="6" t="n">
         <v>1</v>
@@ -10067,7 +10045,7 @@
         <f aca="false">(C74+'Model Parameters'!$B$11)/('Model Parameters'!$B$9+'Model Parameters'!$B$11*'Model Parameters'!$B$10)</f>
         <v>0.00132709146637652</v>
       </c>
-      <c r="E74" s="13" t="n">
+      <c r="E74" s="12" t="n">
         <f aca="false">B74*LN(D74)</f>
         <v>-6.62476559882091</v>
       </c>
@@ -10078,7 +10056,7 @@
         <f aca="false">(F74+'Model Parameters'!$C$11)/('Model Parameters'!$C$9+'Model Parameters'!$C$11*'Model Parameters'!$C$10)</f>
         <v>1.12823648739365E-006</v>
       </c>
-      <c r="H74" s="13" t="n">
+      <c r="H74" s="12" t="n">
         <f aca="false">B74*LN(G74)</f>
         <v>-13.6948547749176</v>
       </c>
@@ -10089,7 +10067,7 @@
         <f aca="false">(I74+'Model Parameters'!$D$11)/('Model Parameters'!$D$9+'Model Parameters'!$D$11*'Model Parameters'!$D$10)</f>
         <v>4.40862680092405E-006</v>
       </c>
-      <c r="K74" s="13" t="n">
+      <c r="K74" s="12" t="n">
         <f aca="false">B74*LN(J74)</f>
         <v>-12.3319473000057</v>
       </c>
@@ -10126,7 +10104,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -10135,7 +10113,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -10151,19 +10129,19 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>31</v>
-      </c>
       <c r="E4" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="81.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10179,182 +10157,182 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>328</v>
-      </c>
-      <c r="B6" s="13" t="n">
+        <v>326</v>
+      </c>
+      <c r="B6" s="12" t="n">
         <f aca="false">'Model Parameters'!B7</f>
         <v>0.3333</v>
       </c>
-      <c r="C6" s="13" t="n">
+      <c r="C6" s="12" t="n">
         <f aca="false">'Model Parameters'!C7</f>
         <v>0.3333</v>
       </c>
-      <c r="D6" s="13" t="n">
+      <c r="D6" s="12" t="n">
         <f aca="false">'Model Parameters'!D7</f>
         <v>0.3334</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B7" s="13" t="n">
+        <v>37</v>
+      </c>
+      <c r="B7" s="12" t="n">
         <f aca="false">'Model Parameters'!B8</f>
         <v>-1.09871229366844</v>
       </c>
-      <c r="C7" s="13" t="n">
+      <c r="C7" s="12" t="n">
         <f aca="false">'Model Parameters'!C8</f>
         <v>-1.09871229366844</v>
       </c>
-      <c r="D7" s="13" t="n">
+      <c r="D7" s="12" t="n">
         <f aca="false">'Model Parameters'!D8</f>
         <v>-1.09841230866544</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>329</v>
-      </c>
-      <c r="B8" s="13" t="n">
+        <v>327</v>
+      </c>
+      <c r="B8" s="12" t="n">
         <f aca="false">SUM('Token Table'!E7:E74)</f>
         <v>-728.963004851643</v>
       </c>
-      <c r="C8" s="13" t="n">
+      <c r="C8" s="12" t="n">
         <f aca="false">SUM('Token Table'!H7:H74)</f>
         <v>-1130.04481150686</v>
       </c>
-      <c r="D8" s="13" t="n">
+      <c r="D8" s="12" t="n">
         <f aca="false">SUM('Token Table'!K7:K74)</f>
         <v>-1001.976445043</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>331</v>
-      </c>
-      <c r="B9" s="13" t="n">
+        <v>329</v>
+      </c>
+      <c r="B9" s="12" t="n">
         <f aca="false">B7+B8</f>
         <v>-730.061717145312</v>
       </c>
-      <c r="C9" s="13" t="n">
+      <c r="C9" s="12" t="n">
         <f aca="false">C7+C8</f>
         <v>-1131.14352380053</v>
       </c>
-      <c r="D9" s="13" t="n">
+      <c r="D9" s="12" t="n">
         <f aca="false">D7+D8</f>
         <v>-1003.07485735166</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>333</v>
-      </c>
-      <c r="B10" s="13" t="n">
+        <v>331</v>
+      </c>
+      <c r="B10" s="12" t="n">
         <f aca="false">SUM('Token Table'!B7:B74)</f>
         <v>141</v>
       </c>
-      <c r="C10" s="13" t="n">
+      <c r="C10" s="12" t="n">
         <f aca="false">B10</f>
         <v>141</v>
       </c>
-      <c r="D10" s="13" t="n">
+      <c r="D10" s="12" t="n">
         <f aca="false">B10</f>
         <v>141</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="81.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>335</v>
-      </c>
-      <c r="B11" s="13" t="n">
+        <v>333</v>
+      </c>
+      <c r="B11" s="12" t="n">
         <f aca="false">B9/B10</f>
         <v>-5.17774267478945</v>
       </c>
-      <c r="C11" s="13" t="n">
+      <c r="C11" s="12" t="n">
         <f aca="false">C9/C10</f>
         <v>-8.02229449503921</v>
       </c>
-      <c r="D11" s="13" t="n">
+      <c r="D11" s="12" t="n">
         <f aca="false">D9/D10</f>
         <v>-7.11400608050825</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>337</v>
-      </c>
-      <c r="B12" s="13" t="n">
+        <v>335</v>
+      </c>
+      <c r="B12" s="12" t="n">
         <f aca="false">MAX(B11:D11)</f>
         <v>-5.17774267478945</v>
       </c>
-      <c r="C12" s="13" t="n">
+      <c r="C12" s="12" t="n">
         <f aca="false">B12</f>
         <v>-5.17774267478945</v>
       </c>
-      <c r="D12" s="13" t="n">
+      <c r="D12" s="12" t="n">
         <f aca="false">B12</f>
         <v>-5.17774267478945</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>339</v>
-      </c>
-      <c r="B13" s="13" t="n">
+        <v>337</v>
+      </c>
+      <c r="B13" s="12" t="n">
         <f aca="false">EXP((B11-B12)/'Model Parameters'!B12)</f>
         <v>1</v>
       </c>
-      <c r="C13" s="13" t="n">
+      <c r="C13" s="12" t="n">
         <f aca="false">EXP((C11-C12)/'Model Parameters'!C12)</f>
         <v>6.65478769466083E-007</v>
       </c>
-      <c r="D13" s="13" t="n">
+      <c r="D13" s="12" t="n">
         <f aca="false">EXP((D11-D12)/'Model Parameters'!D12)</f>
         <v>6.24392153665962E-005</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="81.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>341</v>
-      </c>
-      <c r="B14" s="14" t="n">
+        <v>339</v>
+      </c>
+      <c r="B14" s="13" t="n">
         <f aca="false">B13/SUM($B$13:$D$13)</f>
         <v>0.999936899287815</v>
       </c>
-      <c r="C14" s="14" t="n">
+      <c r="C14" s="13" t="n">
         <f aca="false">C13/SUM($B$13:$D$13)</f>
         <v>6.65436777281786E-007</v>
       </c>
-      <c r="D14" s="14" t="n">
+      <c r="D14" s="13" t="n">
         <f aca="false">D13/SUM($B$13:$D$13)</f>
         <v>6.24352754076383E-005</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10366,7 +10344,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B16" s="6" t="str">
         <f aca="false">INDEX($B$4:$D$4,1,MATCH(MAX(B9:D9),B9:D9,0))</f>
@@ -10375,12 +10353,12 @@
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
       <c r="E16" s="6" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B17" s="6" t="str">
         <f aca="false">IF(OR(B16="Fraud",B16="Injection"),"MALICIOUS","SAFE")</f>
@@ -10389,7 +10367,7 @@
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
       <c r="E17" s="6" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
   </sheetData>
